--- a/research/files/bc_transit_routes.xlsx
+++ b/research/files/bc_transit_routes.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -438,14 +438,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>British Columbia transit routes and stops, for cyclists</t>
+          <t>British Columbia transit routes, for cyclists</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Every scheduled passenger service we have found that a cyclist could use to get around British Columbia, with its ordered stops and their locations. Buses, ferries, inland ferries, water taxis, trains, SkyTrain, flights, ride-share and one-way rental car corridors.</t>
+          <t>Every scheduled passenger service we have found that a cyclist could use to get around British Columbia. Buses, ferries, inland ferries, water taxis, trains, SkyTrain, flights, ride-share and one-way rental car corridors. Its ordered stops and their locations are the companion stops file.</t>
         </is>
       </c>
     </row>
@@ -462,7 +462,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Published 2026-07-25 by BC Cycle Tourism Society.</t>
+          <t>Published 2026-07-26 by BC Cycle Tourism Society.</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Suggested citation: BC Cycle Tourism Society (2026). British Columbia transit routes and stops, for cyclists [data set]. Version 2026-07-25. https://bccycletourism.ca/research/</t>
+          <t>Suggested citation: BC Cycle Tourism Society (2026). British Columbia transit routes, for cyclists [data set]. Version 2026-07-26. https://bccycletourism.ca/research/</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Routes: 282 rows, 14 columns.</t>
+          <t>Routes: 326 rows, 14 columns.</t>
         </is>
       </c>
     </row>
@@ -540,49 +540,56 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>This is topology, not a timetable. We record which services exist, where they stop, and in what order. We do not record when they depart. Because there are no departure times here, this is not General Transit Feed Specification (GTFS) data and cannot be loaded by GTFS tools. Where one of our columns means the same thing as a GTFS field, we have borrowed the GTFS name so it reads familiarly.</t>
+          <t>There is no feed. The registry behind these files is kept by hand, assembled service by service from operator websites, regional transit schedules, tourism listings, ferry timetables, and telephone calls. It is a collection, not a census: we cannot know what we have missed, so treat every count as a floor, never a total.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Of the 282 routes, 223 are part of the network we route journeys across. The rest are published too, each with the reason we set it aside, because what was excluded is part of the picture.</t>
+          <t>This is topology, not a timetable. We record which services exist, where they stop, and in what order. We do not record when they depart. Because there are no departure times here, this is not General Transit Feed Specification (GTFS) data and cannot be loaded by GTFS tools. Where one of our columns means the same thing as a GTFS field, we have borrowed the GTFS name so it reads familiarly.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Of the 326 routes, 267 are part of the network we route journeys across. The rest are published too, each with the reason we set it aside, because what was excluded is part of the picture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Each route's stops, in order, are in the companion stops file.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-    </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>Bicycle policies change, and this is the one place in our research where stale data has a physical cost. A route measurement that goes out of date is a mild embarrassment. A bicycle policy that goes out of date leaves somebody standing at a depot with a loaded bicycle and no way onto the bus. Check the last_verified column before you rely on a row, and confirm with the operator before you travel.</t>
-        </is>
-      </c>
+      <c r="A23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Bicycle policies change, and this is the one place in our research where stale data has a physical cost. A route measurement that goes out of date is a mild embarrassment. A bicycle policy that goes out of date leaves somebody standing at a depot with a loaded bicycle and no way onto the bus. Check the last_verified column in the carriers file before you rely on a row, and confirm with the operator before you travel.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>We do not run any of these services. Operators change their routes, their seasons and their bicycle rules without telling us. Corrections are welcome and we would rather hear about a wrong row than not.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr"/>
-    </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>The research here uses AI assistance (Claude models, Anthropic) for data collection, analysis, and writing. Feel free to ask for more details if you are interested.</t>
         </is>
@@ -599,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N283"/>
+  <dimension ref="A1:N327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1471,7 +1478,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>seasonal-varies</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -5842,7 +5849,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>seasonal-varies</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -5903,7 +5910,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>seasonal-varies</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -5962,6 +5969,11 @@
           <t>Sea-to-Sky</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>seasonal-varies</t>
+        </is>
+      </c>
       <c r="G99" t="n">
         <v>2</v>
       </c>
@@ -6203,7 +6215,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -6369,6 +6381,11 @@
           <t>Southern Interior</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="G106" t="n">
         <v>9</v>
       </c>
@@ -6393,11 +6410,6 @@
           <t>yes, with conditions</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>Continues east into Alberta beyond Golden.</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6547,6 +6559,11 @@
           <t>Southern Interior</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="G109" t="n">
         <v>14</v>
       </c>
@@ -6571,11 +6588,6 @@
           <t>yes, with conditions</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>Continues east into Alberta beyond Field.</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6603,6 +6615,11 @@
           <t>Sea-to-Sky</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>seasonal-varies</t>
+        </is>
+      </c>
       <c r="G110" t="n">
         <v>5</v>
       </c>
@@ -8513,7 +8530,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>seasonal-varies</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -9142,6 +9159,11 @@
           <t>Vancouver Island</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>seasonal-varies</t>
+        </is>
+      </c>
       <c r="G154" t="n">
         <v>2</v>
       </c>
@@ -9259,6 +9281,11 @@
           <t>West Kootenay</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="G156" t="n">
         <v>2</v>
       </c>
@@ -9315,6 +9342,11 @@
           <t>West Kootenay</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="G157" t="n">
         <v>2</v>
       </c>
@@ -9371,6 +9403,11 @@
           <t>West Kootenay</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="G158" t="n">
         <v>2</v>
       </c>
@@ -9427,6 +9464,11 @@
           <t>West Kootenay</t>
         </is>
       </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="G159" t="n">
         <v>2</v>
       </c>
@@ -9483,6 +9525,11 @@
           <t>Thompson-Nicola</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="G160" t="n">
         <v>2</v>
       </c>
@@ -9539,6 +9586,11 @@
           <t>Bulkley-Nechako</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="G161" t="n">
         <v>2</v>
       </c>
@@ -9595,6 +9647,11 @@
           <t>West Kootenay</t>
         </is>
       </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="G162" t="n">
         <v>2</v>
       </c>
@@ -9651,6 +9708,11 @@
           <t>West Kootenay</t>
         </is>
       </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="G163" t="n">
         <v>2</v>
       </c>
@@ -9707,6 +9769,11 @@
           <t>Lower Mainland</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="G164" t="n">
         <v>2</v>
       </c>
@@ -9763,6 +9830,11 @@
           <t>Thompson-Nicola</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="G165" t="n">
         <v>2</v>
       </c>
@@ -9819,6 +9891,11 @@
           <t>Cariboo</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="G166" t="n">
         <v>2</v>
       </c>
@@ -9875,6 +9952,11 @@
           <t>North Coast</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="G167" t="n">
         <v>2</v>
       </c>
@@ -9931,6 +10013,11 @@
           <t>Thompson-Nicola</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="G168" t="n">
         <v>2</v>
       </c>
@@ -9987,6 +10074,11 @@
           <t>Thompson-Nicola</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="G169" t="n">
         <v>2</v>
       </c>
@@ -10043,6 +10135,11 @@
           <t>Metro Vancouver</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>seasonal-varies</t>
+        </is>
+      </c>
       <c r="G170" t="n">
         <v>3</v>
       </c>
@@ -10101,7 +10198,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -10137,7 +10234,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>local-bus:clw-10</t>
+          <t>local-bus:ash-1</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -10152,12 +10249,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>10 Valley Connector</t>
+          <t>1 Ashcroft- Clinton</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Thompson-Nicola</t>
+          <t>Thompson Okanagan</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -10166,16 +10263,16 @@
         </is>
       </c>
       <c r="G172" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Kamloops</t>
+          <t>Ashcroft</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Clearwater</t>
+          <t>Clinton</t>
         </is>
       </c>
       <c r="J172" t="b">
@@ -10187,13 +10284,18 @@
       <c r="M172" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Runs Wednesday and Friday only.</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>local-bus:cv-1</t>
+          <t>local-bus:clw-1</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -10208,17 +10310,17 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>1 Comox Mall / Anfield Centre via N.I.C.</t>
+          <t>1 Vavenby</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Thompson Okanagan</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -10226,12 +10328,12 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Comox</t>
+          <t>Clearwater</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Courtenay</t>
+          <t>Vavenby</t>
         </is>
       </c>
       <c r="J173" t="b">
@@ -10243,13 +10345,18 @@
       <c r="M173" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Weekdays only.</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>local-bus:cv-10</t>
+          <t>local-bus:clw-10</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -10264,17 +10371,17 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>10 Fanny Bay / Deep Bay / Downtown Courtenay</t>
+          <t>10 Valley Connector</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Thompson-Nicola</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -10282,12 +10389,12 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Courtenay</t>
+          <t>Kamloops</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Buckley Bay</t>
+          <t>Clearwater</t>
         </is>
       </c>
       <c r="J174" t="b">
@@ -10299,18 +10406,13 @@
       <c r="M174" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>Only two trips on Sundays.</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>local-bus:cv-11</t>
+          <t>local-bus:cv-1</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -10325,7 +10427,7 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>11 Airport via Powell R. Ferry / Downtown</t>
+          <t>1 Comox Mall / Anfield Centre via N.I.C.</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -10335,11 +10437,11 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
@@ -10360,18 +10462,13 @@
       <c r="M175" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>One loop serves both the Little River ferry terminal and Comox airport; about 5–7 trips a day, and Sunday service is unconfirmed.</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>local-bus:cvt-34</t>
+          <t>local-bus:cv-10</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -10386,7 +10483,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>34 Ladysmith-Chemainus</t>
+          <t>10 Fanny Bay / Deep Bay / Downtown Courtenay</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10396,7 +10493,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -10404,12 +10501,12 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Ladysmith</t>
+          <t>Courtenay</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>North Cowichan</t>
+          <t>Buckley Bay</t>
         </is>
       </c>
       <c r="J176" t="b">
@@ -10421,13 +10518,18 @@
       <c r="M176" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Only two trips on Sundays.</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>local-bus:cvt-36</t>
+          <t>local-bus:cv-11</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -10442,7 +10544,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>36 Ladysmith-Duncan Express</t>
+          <t>11 Airport via Powell R. Ferry / Downtown</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10460,12 +10562,12 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Ladysmith</t>
+          <t>Comox</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Duncan</t>
+          <t>Courtenay</t>
         </is>
       </c>
       <c r="J177" t="b">
@@ -10477,13 +10579,18 @@
       <c r="M177" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>One loop serves both the Little River ferry terminal and Comox airport; about 5–7 trips a day, and Sunday service is unconfirmed.</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>local-bus:cvt-6</t>
+          <t>local-bus:cv-12</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -10498,7 +10605,7 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>6 Crofton-Chemainus</t>
+          <t>12 Oyster River / Downtown Courtenay</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10508,7 +10615,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -10516,12 +10623,12 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>North Cowichan</t>
+          <t>Oyster River</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Duncan</t>
+          <t>Courtenay</t>
         </is>
       </c>
       <c r="J178" t="b">
@@ -10533,13 +10640,18 @@
       <c r="M178" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>No service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>local-bus:cvt-66</t>
+          <t>local-bus:cvt-34</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -10554,7 +10666,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>66 CVX Cowichan - Victoria Express</t>
+          <t>34 Ladysmith-Chemainus</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10564,15 +10676,15 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G179" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Duncan</t>
+          <t>Ladysmith</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -10595,7 +10707,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>local-bus:ea-goose</t>
+          <t>local-bus:cvt-36</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -10605,12 +10717,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Electric Alpine Biking</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Galloping Goose Trail shuttle</t>
+          <t>36 Ladysmith-Duncan Express</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10628,12 +10740,12 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>View Royal</t>
+          <t>Ladysmith</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Sooke</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="J180" t="b">
@@ -10644,14 +10756,14 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>local-bus:ek-22</t>
+          <t>local-bus:cvt-6</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -10666,17 +10778,17 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>22 KC Commuter</t>
+          <t>6 Crofton-Chemainus</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Kootenay</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -10684,12 +10796,12 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Cranbrook</t>
+          <t>North Cowichan</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Kimberley</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="J181" t="b">
@@ -10707,7 +10819,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>local-bus:fv-21</t>
+          <t>local-bus:cvt-66</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -10722,12 +10834,12 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>21 Fraser Hwy</t>
+          <t>66 CVX Cowichan - Victoria Express</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Metro Vancouver / Fraser Valley</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -10736,16 +10848,16 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Langley</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Abbotsford</t>
+          <t>North Cowichan</t>
         </is>
       </c>
       <c r="J182" t="b">
@@ -10763,7 +10875,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>local-bus:fv-21a</t>
+          <t>local-bus:cvt-7</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -10778,17 +10890,17 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>21A Fraser Hwy</t>
+          <t>7 Cowichan Lake</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Metro Vancouver / Fraser Valley</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -10796,12 +10908,12 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Langley</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Abbotsford</t>
+          <t>Lake Cowichan</t>
         </is>
       </c>
       <c r="J183" t="b">
@@ -10819,7 +10931,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>local-bus:fv-31</t>
+          <t>local-bus:cvt-8</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -10834,12 +10946,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>31 Valley Connector</t>
+          <t>8 Mill Bay via Telegraph Rd/Duncan via Shawnigan Lk</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Metro Vancouver / Fraser Valley</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10852,12 +10964,12 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Mission</t>
+          <t>Mill Bay</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Abbotsford</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="J184" t="b">
@@ -10875,7 +10987,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>local-bus:fv-31a</t>
+          <t>local-bus:cvt-9</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -10890,12 +11002,12 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>31A Valley Connector</t>
+          <t>9 Mill Bay via Shawnigan Lk/Duncan via Telegraph Rd</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Metro Vancouver / Fraser Valley</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -10908,12 +11020,12 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Mission</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>Abbotsford</t>
+          <t>Mill Bay</t>
         </is>
       </c>
       <c r="J185" t="b">
@@ -10931,7 +11043,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>local-bus:fv-31x</t>
+          <t>local-bus:cvt-99</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -10946,12 +11058,12 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>31X Valley Connector</t>
+          <t>99 SVX Shawnigan Lake - Victoria Express</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Metro Vancouver / Fraser Valley</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -10960,16 +11072,16 @@
         </is>
       </c>
       <c r="G186" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Abbotsford</t>
+          <t>Cobble Hill</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Mission</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="J186" t="b">
@@ -10981,13 +11093,18 @@
       <c r="M186" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Weekdays only.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>local-bus:fv-55</t>
+          <t>local-bus:ea-goose</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -10997,35 +11114,35 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>BC Transit</t>
+          <t>Electric Alpine Biking</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>55 Yarrow - Greendale</t>
+          <t>Galloping Goose Trail shuttle</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Metro Vancouver / Fraser Valley</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>on-demand</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Chilliwack</t>
+          <t>View Royal</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Abbotsford</t>
+          <t>Sooke</t>
         </is>
       </c>
       <c r="J187" t="b">
@@ -11036,14 +11153,14 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>local-bus:fv-66</t>
+          <t>local-bus:ek-22</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11058,30 +11175,30 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>66 Fraser Valley Express</t>
+          <t>22 KC Commuter</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Metro Vancouver / Fraser Valley</t>
+          <t>Kootenay</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Chilliwack</t>
+          <t>Cranbrook</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Burnaby</t>
+          <t>Kimberley</t>
         </is>
       </c>
       <c r="J188" t="b">
@@ -11099,7 +11216,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>local-bus:fv-71</t>
+          <t>local-bus:ek-31</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11114,17 +11231,17 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>71 Agassiz-Harrison</t>
+          <t>31 South Connector</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Metro Vancouver / Fraser Valley</t>
+          <t>Kootenay Rockies</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -11132,12 +11249,12 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Harrison Hot Springs</t>
+          <t>Invermere</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Chilliwack</t>
+          <t>Canal Flats</t>
         </is>
       </c>
       <c r="J189" t="b">
@@ -11149,13 +11266,18 @@
       <c r="M189" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>Weekdays only.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>local-bus:krt-23</t>
+          <t>local-bus:ek-32</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11170,17 +11292,17 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>23 Lake Country</t>
+          <t>32 North Connector</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Southern Interior</t>
+          <t>Kootenay Rockies</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -11188,12 +11310,12 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Kelowna</t>
+          <t>Invermere</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Kelowna</t>
+          <t>Edgewater</t>
         </is>
       </c>
       <c r="J190" t="b">
@@ -11209,14 +11331,14 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>First leg of the airport–downtown chain; transfer to Route 97 at UBCO Exchange.</t>
+          <t>Weekdays only.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>local-bus:krt-97</t>
+          <t>local-bus:ek-41</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11231,30 +11353,30 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>97 Okanagan</t>
+          <t>41 Fernie / Sparwood / Elkford</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Southern Interior</t>
+          <t>Kootenay Rockies</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G191" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Kelowna</t>
+          <t>Elkford</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Kelowna</t>
+          <t>Fernie</t>
         </is>
       </c>
       <c r="J191" t="b">
@@ -11270,14 +11392,14 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>Second leg of the airport–downtown chain: UBCO Exchange to Queensway downtown.</t>
+          <t>Weekdays only.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>local-bus:mtw-1</t>
+          <t>local-bus:fv-21</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11292,17 +11414,17 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>1/2 Port McNeill - Port Hardy</t>
+          <t>21 Fraser Hwy</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Metro Vancouver / Fraser Valley</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -11310,12 +11432,12 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Port Hardy</t>
+          <t>Langley</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Port McNeill</t>
+          <t>Abbotsford</t>
         </is>
       </c>
       <c r="J192" t="b">
@@ -11327,18 +11449,13 @@
       <c r="M192" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N192" t="inlineStr">
-        <is>
-          <t>Five trips a day on weekdays, two on Saturday, and no service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>local-bus:pg-161</t>
+          <t>local-bus:fv-21a</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11353,12 +11470,12 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>161 Prince George / Burns Lake</t>
+          <t>21A Fraser Hwy</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Cariboo</t>
+          <t>Metro Vancouver / Fraser Valley</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -11371,12 +11488,12 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Vanderhoof</t>
+          <t>Langley</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Prince George</t>
+          <t>Abbotsford</t>
         </is>
       </c>
       <c r="J193" t="b">
@@ -11394,7 +11511,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>local-bus:plr-12</t>
+          <t>local-bus:fv-31</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11409,17 +11526,17 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>12 Stillwater</t>
+          <t>31 Valley Connector</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>qathet (Powell River) / Sunshine Coast</t>
+          <t>Metro Vancouver / Fraser Valley</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -11427,12 +11544,12 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>Mission</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Powell River</t>
+          <t>Abbotsford</t>
         </is>
       </c>
       <c r="J194" t="b">
@@ -11450,7 +11567,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>local-bus:pmb-99</t>
+          <t>local-bus:fv-31a</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -11465,12 +11582,12 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>99 Pemberton Commuter</t>
+          <t>31A Valley Connector</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Sea-to-Sky</t>
+          <t>Metro Vancouver / Fraser Valley</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -11479,16 +11596,16 @@
         </is>
       </c>
       <c r="G195" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Whistler</t>
+          <t>Mission</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Pemberton</t>
+          <t>Abbotsford</t>
         </is>
       </c>
       <c r="J195" t="b">
@@ -11506,7 +11623,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>local-bus:pr-55</t>
+          <t>local-bus:fv-31x</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -11521,12 +11638,12 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>55 Fairview Bay</t>
+          <t>31X Valley Connector</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Metro Vancouver / Fraser Valley</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -11539,12 +11656,12 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Abbotsford</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Mission</t>
         </is>
       </c>
       <c r="J196" t="b">
@@ -11556,18 +11673,13 @@
       <c r="M196" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr">
-        <is>
-          <t>Monday to Saturday only, about three trips a day; stops near the ferry terminal.</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>local-bus:qnl-30</t>
+          <t>local-bus:fv-55</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -11582,12 +11694,12 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>30 Wells</t>
+          <t>55 Yarrow - Greendale</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Cariboo</t>
+          <t>Metro Vancouver / Fraser Valley</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -11600,12 +11712,12 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Quesnel</t>
+          <t>Chilliwack</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Barkerville</t>
+          <t>Abbotsford</t>
         </is>
       </c>
       <c r="J197" t="b">
@@ -11623,7 +11735,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>local-bus:rdn-1</t>
+          <t>local-bus:fv-66</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -11638,12 +11750,12 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>1 Nanaimo Rapid Line</t>
+          <t>66 Fraser Valley Express</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Metro Vancouver / Fraser Valley</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -11652,16 +11764,16 @@
         </is>
       </c>
       <c r="G198" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Chilliwack</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Burnaby</t>
         </is>
       </c>
       <c r="J198" t="b">
@@ -11673,18 +11785,13 @@
       <c r="M198" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N198" t="inlineStr">
-        <is>
-          <t>Runs every 20 minutes or so, seven days a week.</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>local-bus:rdn-20</t>
+          <t>local-bus:fv-71</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -11699,12 +11806,12 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>20/20A Hammond Bay / Dover</t>
+          <t>71 Agassiz-Harrison</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Metro Vancouver / Fraser Valley</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -11717,12 +11824,12 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Harrison Hot Springs</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Chilliwack</t>
         </is>
       </c>
       <c r="J199" t="b">
@@ -11740,7 +11847,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>local-bus:rdn-25</t>
+          <t>local-bus:fv-72</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -11755,17 +11862,17 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>25 Ferry Shuttle</t>
+          <t>72 Hope</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Vancouver, Coast &amp; Mountains</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -11773,12 +11880,12 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Hope</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="J200" t="b">
@@ -11794,14 +11901,14 @@
       </c>
       <c r="N200" t="inlineStr">
         <is>
-          <t>Also serves the Hullo ferry and Helijet terminals at the Nanaimo Port Authority.</t>
+          <t>No service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>local-bus:rdn-70</t>
+          <t>local-bus:krt-23</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -11816,12 +11923,12 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>70 NCX Nanaimo - Cowichan Express</t>
+          <t>23 Lake Country</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Southern Interior</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -11830,16 +11937,16 @@
         </is>
       </c>
       <c r="G201" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Kelowna</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Duncan</t>
+          <t>Kelowna</t>
         </is>
       </c>
       <c r="J201" t="b">
@@ -11851,13 +11958,18 @@
       <c r="M201" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>First leg of the airport–downtown chain; transfer to Route 97 at UBCO Exchange.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>local-bus:rdn-9</t>
+          <t>local-bus:krt-97</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -11872,12 +11984,12 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>9 Intercity</t>
+          <t>97 Okanagan</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Southern Interior</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -11886,16 +11998,16 @@
         </is>
       </c>
       <c r="G202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Qualicum Beach</t>
+          <t>Kelowna</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Kelowna</t>
         </is>
       </c>
       <c r="J202" t="b">
@@ -11907,13 +12019,18 @@
       <c r="M202" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>Second leg of the airport–downtown chain: UBCO Exchange to Queensway downtown.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>local-bus:sc-1</t>
+          <t>local-bus:mtw-1</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -11928,17 +12045,17 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>1 Sechelt-Gibsons/Langdale Ferry</t>
+          <t>1/2 Port McNeill - Port Hardy</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Sunshine Coast</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -11946,12 +12063,12 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Gibsons</t>
+          <t>Port Hardy</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Sechelt</t>
+          <t>Port McNeill</t>
         </is>
       </c>
       <c r="J203" t="b">
@@ -11963,13 +12080,18 @@
       <c r="M203" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>Five trips a day on weekdays, two on Saturday, and no service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>local-bus:sc-90</t>
+          <t>local-bus:mtw-5</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -11984,17 +12106,17 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>90 Sechelt-Gibsons/Langdale Ferry Express</t>
+          <t>5 Coal Harbour</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Sunshine Coast</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -12002,12 +12124,12 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Sechelt</t>
+          <t>Port Hardy</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Gibsons</t>
+          <t>Coal Harbour</t>
         </is>
       </c>
       <c r="J204" t="b">
@@ -12019,13 +12141,18 @@
       <c r="M204" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>No service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>local-bus:skn-11</t>
+          <t>local-bus:pg-161</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12040,12 +12167,12 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>11 Terrace-Kitimat Connector</t>
+          <t>161 Prince George / Burns Lake</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>North Coast</t>
+          <t>Cariboo</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -12058,12 +12185,12 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Terrace</t>
+          <t>Vanderhoof</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Kitimat</t>
+          <t>Prince George</t>
         </is>
       </c>
       <c r="J205" t="b">
@@ -12081,7 +12208,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>local-bus:sok-30</t>
+          <t>local-bus:pg-162</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12096,12 +12223,12 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>30 Penticton / Summerland</t>
+          <t>162 Smithers / Burns Lake</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Southern Interior</t>
+          <t>Northern BC</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -12114,12 +12241,12 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Penticton</t>
+          <t>Smithers</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Summerland</t>
+          <t>Burns Lake</t>
         </is>
       </c>
       <c r="J206" t="b">
@@ -12131,13 +12258,18 @@
       <c r="M206" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>Runs Monday, Wednesday and Friday only.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>local-bus:sok-40</t>
+          <t>local-bus:plr-12</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12152,12 +12284,12 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>40 Osoyoos / Penticton</t>
+          <t>12 Stillwater</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Southern Interior</t>
+          <t>qathet (Powell River) / Sunshine Coast</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -12166,16 +12298,16 @@
         </is>
       </c>
       <c r="G207" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Osoyoos</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Penticton</t>
+          <t>Powell River</t>
         </is>
       </c>
       <c r="J207" t="b">
@@ -12193,7 +12325,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>local-bus:sok-50</t>
+          <t>local-bus:plr-13</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12208,12 +12340,12 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>50 Penticton / Princeton</t>
+          <t>13 Texada Island</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Southern Interior</t>
+          <t>Vancouver, Coast &amp; Mountains</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -12222,16 +12354,16 @@
         </is>
       </c>
       <c r="G208" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Princeton</t>
+          <t>Gillies Bay</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Penticton</t>
+          <t>Powell River</t>
         </is>
       </c>
       <c r="J208" t="b">
@@ -12243,13 +12375,18 @@
       <c r="M208" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>Runs Tuesday and Thursday only.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>local-bus:sok-70</t>
+          <t>local-bus:plr-14</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12264,12 +12401,12 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>70 Kelowna / Penticton</t>
+          <t>14 Lund</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Southern Interior</t>
+          <t>qathet (Powell River) / Sunshine Coast</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -12278,16 +12415,16 @@
         </is>
       </c>
       <c r="G209" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Penticton</t>
+          <t>Powell River</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Kelowna</t>
+          <t>Lund</t>
         </is>
       </c>
       <c r="J209" t="b">
@@ -12299,13 +12436,18 @@
       <c r="M209" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>Runs Monday, Tuesday and Friday most of the year, six days a week from mid-May to Labour Day; some stretches are on-request. Front bike rack; e-bikes under 25 kg allowed.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>local-bus:tl-229</t>
+          <t>local-bus:pmb-99</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12315,17 +12457,17 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>TransLink</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>229 Lonsdale Quay / Lynn Valley</t>
+          <t>99 Pemberton Commuter</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Metro Vancouver</t>
+          <t>Sea-to-Sky</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -12334,16 +12476,16 @@
         </is>
       </c>
       <c r="G210" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>North Vancouver</t>
+          <t>Whistler</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>North Vancouver</t>
+          <t>Pemberton</t>
         </is>
       </c>
       <c r="J210" t="b">
@@ -12354,19 +12496,14 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
-        </is>
-      </c>
-      <c r="N210" t="inlineStr">
-        <is>
-          <t>Runs about every 30 minutes, seven days a week.</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>local-bus:tl-257</t>
+          <t>local-bus:pr-55</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12376,35 +12513,35 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>TransLink</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>257 Horseshoe Bay Express</t>
+          <t>55 Fairview Bay</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Metro Vancouver</t>
+          <t>North</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>West Vancouver</t>
+          <t>Prince Rupert</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Prince Rupert</t>
         </is>
       </c>
       <c r="J211" t="b">
@@ -12415,14 +12552,19 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>Monday to Saturday only, about three trips a day; stops near the ferry terminal.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>local-bus:tl-262</t>
+          <t>local-bus:qnl-30</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12432,48 +12574,53 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>TransLink</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>262 Lions Bay-Brunswick (Community Shuttle)</t>
+          <t>30 Wells</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Metro Vancouver</t>
+          <t>Cariboo</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G212" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Quesnel</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Barkerville</t>
+        </is>
       </c>
       <c r="J212" t="b">
-        <v>0</v>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>reviewed and set aside</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L212" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>local-bus:tl-620</t>
+          <t>local-bus:qnl-31</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12483,35 +12630,35 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>TransLink</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>620 Bridgeport Station / Tsawwassen Ferry</t>
+          <t>31 Nazko</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Metro Vancouver</t>
+          <t>Cariboo Chilcotin Coast</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G213" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Delta</t>
+          <t>Quesnel</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Nazko</t>
         </is>
       </c>
       <c r="J213" t="b">
@@ -12522,19 +12669,19 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>The 620 is year-round, roughly hourly, timed to sailings, with two bike-rack spots. On busy summer ferry days the seasonal 900 Bike Bus can carry an extra 10 bikes.</t>
+          <t>Wednesdays only.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>local-bus:tl-701</t>
+          <t>local-bus:rdn-1</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12544,17 +12691,17 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>TransLink</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>701 Coquitlam Central / Haney Place (daily core)</t>
+          <t>1 Nanaimo Rapid Line</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Metro Vancouver</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -12567,12 +12714,12 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Coquitlam</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Maple Ridge</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="J214" t="b">
@@ -12583,19 +12730,19 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>Daily including weekends, about every 15–30 minutes.</t>
+          <t>Runs every 20 minutes or so, seven days a week.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>local-bus:tl-701-mission</t>
+          <t>local-bus:rdn-20</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12605,22 +12752,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>TransLink</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>701 Haney Place / Mission City (weekday-only extension)</t>
+          <t>20/20A Hammond Bay / Dover</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Metro Vancouver</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -12628,12 +12775,12 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Maple Ridge</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Mission</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="J215" t="b">
@@ -12644,19 +12791,14 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
-        </is>
-      </c>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>Weekday-only extension; it doesn't run on weekends, when the West Coast Express is also dark.</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>local-bus:tl-r2</t>
+          <t>local-bus:rdn-25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12666,17 +12808,17 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>TransLink</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>R2 Marine Dr RapidBus</t>
+          <t>25 Ferry Shuttle</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Metro Vancouver</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -12689,12 +12831,12 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>North Vancouver</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>West Vancouver</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="J216" t="b">
@@ -12705,19 +12847,19 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>Frequent service, seven days a week.</t>
+          <t>Also serves the Hullo ferry and Helijet terminals at the Nanaimo Port Authority.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>local-bus:vrt-61</t>
+          <t>local-bus:rdn-70</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12732,7 +12874,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>61 Sooke / Langford / Downtown</t>
+          <t>70 NCX Nanaimo - Cowichan Express</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -12746,16 +12888,16 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Sooke</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="J217" t="b">
@@ -12773,7 +12915,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>local-bus:vrt-64</t>
+          <t>local-bus:rdn-9</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12788,7 +12930,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>64 Langford Exch / Sooke via E Sooke and Beecher Bay</t>
+          <t>9 Intercity</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -12798,7 +12940,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -12806,12 +12948,12 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Sooke</t>
+          <t>Qualicum Beach</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Colwood</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="J218" t="b">
@@ -12829,7 +12971,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>local-bus:vrt-65</t>
+          <t>local-bus:rdn-99</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12844,7 +12986,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>65 Sooke / Downtown via Westhills</t>
+          <t>99 Deep Bay</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -12854,20 +12996,20 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G219" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Qualicum Beach</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Sooke</t>
+          <t>Deep Bay</t>
         </is>
       </c>
       <c r="J219" t="b">
@@ -12885,7 +13027,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>local-bus:vrt-70</t>
+          <t>local-bus:sc-1</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12900,12 +13042,12 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>70 Swartz Bay / Downtown</t>
+          <t>1 Sechelt-Gibsons/Langdale Ferry</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Sunshine Coast</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -12918,12 +13060,12 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Gibsons</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Sechelt</t>
         </is>
       </c>
       <c r="J220" t="b">
@@ -12941,7 +13083,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>local-bus:vrt-72</t>
+          <t>local-bus:sc-4</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12956,12 +13098,12 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>72 Swartz Bay / Downtown (via Saanichton)</t>
+          <t>4 Halfmoon Bay</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Vancouver, Coast &amp; Mountains</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -12974,12 +13116,12 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Sechelt</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Halfmoon Bay</t>
         </is>
       </c>
       <c r="J221" t="b">
@@ -12991,18 +13133,13 @@
       <c r="M221" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N221" t="inlineStr">
-        <is>
-          <t>Via Saanichton; a parallel option to the 70.</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>local-bus:vs-90</t>
+          <t>local-bus:sc-90</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13017,12 +13154,12 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>90 UBCO/Vernon</t>
+          <t>90 Sechelt-Gibsons/Langdale Ferry Express</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Southern Interior</t>
+          <t>Sunshine Coast</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -13031,16 +13168,16 @@
         </is>
       </c>
       <c r="G222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Kelowna</t>
+          <t>Sechelt</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Vernon</t>
+          <t>Gibsons</t>
         </is>
       </c>
       <c r="J222" t="b">
@@ -13058,7 +13195,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>local-bus:wct-1</t>
+          <t>local-bus:skn-11</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -13068,35 +13205,35 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>West Coast Transit System (Tofino/Ucluelet)</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>1 Tofino / Ucluelet</t>
+          <t>11 Terrace-Kitimat Connector</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>North Coast</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G223" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Ucluelet</t>
+          <t>Terrace</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Tofino</t>
+          <t>Kitimat</t>
         </is>
       </c>
       <c r="J223" t="b">
@@ -13114,7 +13251,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>local-bus:wk-45</t>
+          <t>local-bus:skn-14</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -13129,12 +13266,12 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>45 Teck</t>
+          <t>14 Gitaus/Queensway</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>West Kootenay</t>
+          <t>Northern BC</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -13147,12 +13284,12 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Rossland</t>
+          <t>Terrace</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Trail</t>
+          <t>Usk</t>
         </is>
       </c>
       <c r="J224" t="b">
@@ -13164,13 +13301,18 @@
       <c r="M224" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>No service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>local-bus:wk-46</t>
+          <t>local-bus:skn-163</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -13185,12 +13327,12 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>46 Rossland</t>
+          <t>163 Hazeltons/Smithers</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>West Kootenay</t>
+          <t>Northern BC</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -13203,12 +13345,12 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Trail</t>
+          <t>Smithers</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Rossland</t>
+          <t>Kispiox</t>
         </is>
       </c>
       <c r="J225" t="b">
@@ -13220,13 +13362,18 @@
       <c r="M225" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>Runs Monday, Wednesday and Friday only.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>local-bus:wk-98</t>
+          <t>local-bus:skn-164</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -13241,12 +13388,12 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>98 Columbia Connector</t>
+          <t>164 Hazeltons/Terrace</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>West Kootenay</t>
+          <t>Northern BC</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -13255,16 +13402,16 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Castlegar</t>
+          <t>Terrace</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Trail</t>
+          <t>Kispiox</t>
         </is>
       </c>
       <c r="J226" t="b">
@@ -13276,13 +13423,18 @@
       <c r="M226" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>Runs Tuesday, Thursday and Saturday only.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>local-bus:wk-99</t>
+          <t>local-bus:skn-31</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -13297,12 +13449,12 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>99 Kootenay Connector</t>
+          <t>31 Gitsegukla</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>West Kootenay</t>
+          <t>Northern BC</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -13315,12 +13467,12 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Nelson</t>
+          <t>Kitseguecla</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Castlegar</t>
+          <t>Kispiox</t>
         </is>
       </c>
       <c r="J227" t="b">
@@ -13332,33 +13484,38 @@
       <c r="M227" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>Runs Tuesday, Thursday and Saturday only.</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>local-train:WCE</t>
+          <t>local-bus:skn-32</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>local-train</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>TransLink (West Coast Express)</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>West Coast Express</t>
+          <t>32 West Connector</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Metro Vancouver / Fraser Valley</t>
+          <t>Northern BC</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -13367,16 +13524,16 @@
         </is>
       </c>
       <c r="G228" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Hazelton</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Mission</t>
+          <t>Kitwanga</t>
         </is>
       </c>
       <c r="J228" t="b">
@@ -13387,39 +13544,44 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>Weekdays only, peak direction only: five trains toward Vancouver in the morning, five back in the evening.</t>
+          <t>Runs Monday, Wednesday and Friday only.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>rental:bud-cr-nan</t>
+          <t>local-bus:smi-23</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>rental-car</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Budget</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>One-way rental: Campbell River – Nanaimo</t>
+          <t>23 Smithers/Witset</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Northern BC</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -13427,50 +13589,60 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Campbell River</t>
+          <t>Moricetown</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Smithers</t>
         </is>
       </c>
       <c r="J229" t="b">
         <v>1</v>
       </c>
       <c r="L229" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>No service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>rental:bud-nan-vic</t>
+          <t>local-bus:sok-30</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>rental-car</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Budget</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>One-way rental: Nanaimo – Victoria</t>
+          <t>30 Penticton / Summerland</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Southern Interior</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -13478,203 +13650,223 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Penticton</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Summerland</t>
         </is>
       </c>
       <c r="J230" t="b">
         <v>1</v>
       </c>
       <c r="L230" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>rental:bud-pa-nan</t>
+          <t>local-bus:sok-40</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>rental-car</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Budget</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>One-way rental: Port Alberni – Nanaimo</t>
+          <t>40 Osoyoos / Penticton</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Southern Interior</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G231" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Port Alberni</t>
+          <t>Osoyoos</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Penticton</t>
         </is>
       </c>
       <c r="J231" t="b">
         <v>1</v>
       </c>
       <c r="L231" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>rental:bud-ph-nan</t>
+          <t>local-bus:sok-50</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>rental-car</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Budget</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>One-way rental: Port Hardy – Nanaimo</t>
+          <t>50 Penticton / Princeton</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Southern Interior</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G232" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Port Hardy</t>
+          <t>Princeton</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Penticton</t>
         </is>
       </c>
       <c r="J232" t="b">
         <v>1</v>
       </c>
       <c r="L232" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>rental:nat-cr-cx</t>
+          <t>local-bus:sok-70</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>rental-car</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>National Car &amp; Truck Rental (Vancouver Island)</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>One-way rental: Campbell River – Comox</t>
+          <t>70 Kelowna / Penticton</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Southern Interior</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G233" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Campbell River</t>
+          <t>Penticton</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
         <is>
-          <t>Comox</t>
+          <t>Kelowna</t>
         </is>
       </c>
       <c r="J233" t="b">
         <v>1</v>
       </c>
       <c r="L233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>rental:nat-cr-nan</t>
+          <t>local-bus:tl-229</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>rental-car</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>National Car &amp; Truck Rental (Vancouver Island)</t>
+          <t>TransLink</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>One-way rental: Campbell River – Nanaimo</t>
+          <t>229 Lonsdale Quay / Lynn Valley</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Metro Vancouver</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>daily</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -13682,70 +13874,80 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Campbell River</t>
+          <t>North Vancouver</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>North Vancouver</t>
         </is>
       </c>
       <c r="J234" t="b">
         <v>1</v>
       </c>
       <c r="L234" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M234" t="inlineStr">
         <is>
           <t>yes, with conditions</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Runs about every 30 minutes, seven days a week.</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>rental:nat-cr-ph</t>
+          <t>local-bus:tl-257</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>rental-car</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>National Car &amp; Truck Rental (Vancouver Island)</t>
+          <t>TransLink</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>One-way rental: Campbell River – Port Hardy</t>
+          <t>257 Horseshoe Bay Express</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Metro Vancouver</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>daily</t>
         </is>
       </c>
       <c r="G235" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Campbell River</t>
+          <t>West Vancouver</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Port Hardy</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="J235" t="b">
         <v>1</v>
       </c>
       <c r="L235" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M235" t="inlineStr">
         <is>
@@ -13756,44 +13958,44 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>rental:nat-cx-nan</t>
+          <t>local-bus:tl-262</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>rental-car</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>National Car &amp; Truck Rental (Vancouver Island)</t>
+          <t>TransLink</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>One-way rental: Comox – Nanaimo</t>
+          <t>262 Lions Bay-Brunswick (Community Shuttle)</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Metro Vancouver</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>daily</t>
         </is>
       </c>
       <c r="G236" t="n">
-        <v>2</v>
-      </c>
-      <c r="H236" t="inlineStr">
-        <is>
-          <t>Comox</t>
-        </is>
-      </c>
-      <c r="I236" t="inlineStr">
-        <is>
-          <t>Nanaimo</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="J236" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>reviewed and set aside</t>
+        </is>
       </c>
       <c r="L236" t="b">
         <v>0</v>
@@ -13807,78 +14009,93 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>rental:nat-cx-ph</t>
+          <t>local-bus:tl-620</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>rental-car</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>National Car &amp; Truck Rental (Vancouver Island)</t>
+          <t>TransLink</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>One-way rental: Comox – Port Hardy</t>
+          <t>620 Bridgeport Station / Tsawwassen Ferry</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Metro Vancouver</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>daily</t>
         </is>
       </c>
       <c r="G237" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Comox</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
         <is>
-          <t>Port Hardy</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="J237" t="b">
         <v>1</v>
       </c>
       <c r="L237" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
           <t>yes, with conditions</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>The 620 is year-round, roughly hourly, timed to sailings, with two bike-rack spots. On busy summer ferry days the seasonal 900 Bike Bus can carry an extra 10 bikes.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>rental:nat-nan-vic</t>
+          <t>local-bus:tl-701</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>rental-car</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>National Car &amp; Truck Rental (Vancouver Island)</t>
+          <t>TransLink</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>One-way rental: Nanaimo – Victoria</t>
+          <t>701 Coquitlam Central / Haney Place (daily core)</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Metro Vancouver</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>daily</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -13886,50 +14103,60 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Coquitlam</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Maple Ridge</t>
         </is>
       </c>
       <c r="J238" t="b">
         <v>1</v>
       </c>
       <c r="L238" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
           <t>yes, with conditions</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>Daily including weekends, about every 15–30 minutes.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>rental:nat-ph-nan</t>
+          <t>local-bus:tl-701-mission</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>rental-car</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>National Car &amp; Truck Rental (Vancouver Island)</t>
+          <t>TransLink</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>One-way rental: Port Hardy – Nanaimo</t>
+          <t>701 Haney Place / Mission City (weekday-only extension)</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Metro Vancouver</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -13937,35 +14164,40 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Port Hardy</t>
+          <t>Maple Ridge</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Mission</t>
         </is>
       </c>
       <c r="J239" t="b">
         <v>1</v>
       </c>
       <c r="L239" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M239" t="inlineStr">
         <is>
           <t>yes, with conditions</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>Weekday-only extension; it doesn't run on weekends, when the West Coast Express is also dark.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>skytrain:1</t>
+          <t>local-bus:tl-r2</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>skytrain</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -13975,7 +14207,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>SkyTrain (all lines)</t>
+          <t>R2 Marine Dr RapidBus</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -13983,17 +14215,22 @@
           <t>Metro Vancouver</t>
         </is>
       </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="G240" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>North Vancouver</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>West Vancouver</t>
         </is>
       </c>
       <c r="J240" t="b">
@@ -14005,51 +14242,56 @@
       <c r="M240" t="inlineStr">
         <is>
           <t>yes, with conditions</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>Frequent service, seven days a week.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>train:amtrak-cascades</t>
+          <t>local-bus:vrt-51x</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>intercity-train</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Amtrak Cascades</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>Vancouver – Seattle (Cascades)</t>
+          <t>51X Westhills Exch / UVic Express</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>cross-border</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G241" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Vancouver Pacific Central</t>
+          <t>Langford</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Seattle Downtown WA</t>
+          <t>Saanich</t>
         </is>
       </c>
       <c r="J241" t="b">
@@ -14060,57 +14302,57 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>Two daily round trips from Pacific Central; reserve bike space when you book. Passport required.</t>
+          <t>Weekdays only.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>train:via-canadian</t>
+          <t>local-bus:vrt-61</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>intercity-train</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>VIA Rail</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>The Canadian (Vancouver – Kamloops North – Jasper)</t>
+          <t>61 Sooke / Langford / Downtown</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>southwest</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G242" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Vancouver Pacific Central</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Jasper AB</t>
+          <t>Sooke</t>
         </is>
       </c>
       <c r="J242" t="b">
@@ -14121,39 +14363,34 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
-        </is>
-      </c>
-      <c r="N242" t="inlineStr">
-        <is>
-          <t>Two departures a week in season; bikes can be checked on and off at Vancouver and Jasper only.</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>train:via-skeena</t>
+          <t>local-bus:vrt-64</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>intercity-train</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>VIA Rail</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>Skeena (Prince Rupert – Prince George – Jasper)</t>
+          <t>64 Langford Exch / Sooke via E Sooke and Beecher Bay</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>north</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -14162,16 +14399,16 @@
         </is>
       </c>
       <c r="G243" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Sooke</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>Jasper AB</t>
+          <t>Colwood</t>
         </is>
       </c>
       <c r="J243" t="b">
@@ -14182,43 +14419,43 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
-        </is>
-      </c>
-      <c r="N243" t="inlineStr">
-        <is>
-          <t>Three departures a week; the trip includes an overnight stop in Prince George (book your own hotel).</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>water-taxi:wt001</t>
+          <t>local-bus:vrt-65</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Victoria Harbour Ferry</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>Empress Dock – Fisherman's Wharf</t>
+          <t>65 Sooke / Downtown via Westhills</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Capital (Greater Victoria)</t>
+          <t>Vancouver Island</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G244" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
@@ -14227,54 +14464,54 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Esquimalt</t>
+          <t>Sooke</t>
         </is>
       </c>
       <c r="J244" t="b">
-        <v>0</v>
-      </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L244" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>water-taxi:wt002</t>
+          <t>local-bus:vrt-70</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Victoria Harbour Ferry</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>Empress Dock – Selkirk Landing (Gorge)</t>
+          <t>70 Swartz Bay / Downtown</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Capital (Greater Victoria)</t>
+          <t>Vancouver Island</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>daily</t>
         </is>
       </c>
       <c r="G245" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -14283,50 +14520,50 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Victoria (Victoria West)</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="J245" t="b">
-        <v>0</v>
-      </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L245" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>water-taxi:wt003</t>
+          <t>local-bus:vrt-71</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>BLAST (English Bay Launch)</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>Snug Cove – Coal Harbour</t>
+          <t>71 Swartz Bay / Downtown</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Metro Vancouver / Howe Sound</t>
+          <t>Vancouver Island</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -14334,60 +14571,60 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Bowen Island</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Sidney</t>
         </is>
       </c>
       <c r="J246" t="b">
-        <v>0</v>
-      </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t>no longer operating</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L246" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>Weekday commuter water taxi, by reservation.</t>
+          <t>Weekdays only.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>water-taxi:wt004</t>
+          <t>local-bus:vrt-72</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>BLAST (English Bay Launch)</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>Snug Cove – Granville Island</t>
+          <t>72 Swartz Bay / Downtown (via Saanichton)</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Metro Vancouver / Howe Sound</t>
+          <t>Vancouver Island</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>daily</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -14395,65 +14632,60 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Bowen Island</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="J247" t="b">
-        <v>0</v>
-      </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>no longer operating</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L247" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>Summer-weekend service to Granville Island.</t>
+          <t>Via Saanichton; a parallel option to the 70.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>water-taxi:wt005</t>
+          <t>local-bus:vrt-75</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Cormorant Marine Water Taxi</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>Horseshoe Bay – Snug Cove</t>
+          <t>75 Saanichton / Royal Oak / Downtown</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Metro Vancouver / Howe Sound</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>on-demand</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -14461,55 +14693,55 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>West Vancouver</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Bowen Island</t>
+          <t>Central Saanich</t>
         </is>
       </c>
       <c r="J248" t="b">
-        <v>0</v>
-      </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L248" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>water-taxi:wt006</t>
+          <t>local-bus:vrt-76</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Cormorant Marine Water Taxi</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>Horseshoe Bay – Gambier Harbour</t>
+          <t>76 Swartz Bay / UVic</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Metro Vancouver / Howe Sound</t>
+          <t>Vancouver Island</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -14517,55 +14749,60 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>West Vancouver</t>
+          <t>North Saanich</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Gambier Island</t>
+          <t>Saanich</t>
         </is>
       </c>
       <c r="J249" t="b">
-        <v>0</v>
-      </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L249" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>Toward Swartz Bay it runs Friday only; toward UVic, Sunday and Monday only.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>water-taxi:wt007</t>
+          <t>local-bus:vrt-83</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Lund Water Taxi</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>Lund – Savary Island</t>
+          <t>83 Sidney / Brentwood / Royal Oak</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>qathet (Powell River) / Sunshine Coast</t>
+          <t>Vancouver Island</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>daily</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -14573,12 +14810,12 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Lund</t>
+          <t>Sidney</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
         <is>
-          <t>Savary Island</t>
+          <t>Saanich</t>
         </is>
       </c>
       <c r="J250" t="b">
@@ -14589,39 +14826,39 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="N250" t="inlineStr">
-        <is>
-          <t>Year-round walk-on service, near-hourly in July and August; reservations required.</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>water-taxi:wt008</t>
+          <t>local-bus:vs-41</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Savary Island Ferry (Finn Bay Marine / Access Point Marine)</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Lund – Savary Island</t>
+          <t>41 Salmon Arm-Enderby</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>qathet (Powell River) / Sunshine Coast</t>
+          <t>Thompson Okanagan</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -14629,60 +14866,60 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Lund</t>
+          <t>Enderby</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Savary Island</t>
+          <t>Salmon Arm</t>
         </is>
       </c>
       <c r="J251" t="b">
-        <v>0</v>
-      </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t>no longer operating</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L251" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
         <is>
-          <t>Departures about every 30 minutes, June to September, from behind the Lund Hotel; reservations required.</t>
+          <t>Wednesdays only.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>water-taxi:wt009</t>
+          <t>local-bus:vs-42</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Discovery Launch Water Taxi</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>Campbell River – Cortes Island</t>
+          <t>42 Salmon Arm-Eagle Bay</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Strathcona / Discovery Islands</t>
+          <t>Thompson Okanagan</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -14690,12 +14927,12 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Campbell River</t>
+          <t>Salmon Arm</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
         <is>
-          <t>Cortes Island</t>
+          <t>Carlin</t>
         </is>
       </c>
       <c r="J252" t="b">
@@ -14706,52 +14943,57 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>Scheduled Fridays and Sundays in summer (also calls at Savary, Hernando and Lund); otherwise by charter.</t>
+          <t>Thursdays only.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>water-taxi:wt010</t>
+          <t>local-bus:vs-43</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Qaya Way West Transportation</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>Campbell River – Savary Island</t>
+          <t>43 Salmon Arm-Sorrento</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Strathcona / Discovery Islands</t>
+          <t>Thompson Okanagan</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G253" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Campbell River</t>
+          <t>Salmon Arm</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Savary Island</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="J253" t="b">
@@ -14762,52 +15004,57 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
         <is>
-          <t>Southern run daily June 26 to September 7, calling at Manson's Landing and Hernando; reservations required.</t>
+          <t>Thursdays only.</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>water-taxi:wt011</t>
+          <t>local-bus:vs-60</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Ahous Hakuum (MHSS)</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>Tofino – Maaqutusiis (Ahousaht)</t>
+          <t>60 Enderby/Vernon</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Alberni-Clayoquot (West Coast Vancouver Island)</t>
+          <t>Thompson Okanagan</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G254" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Tofino</t>
+          <t>Enderby</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Ahousaht (Flores Island)</t>
+          <t>Vernon</t>
         </is>
       </c>
       <c r="J254" t="b">
@@ -14818,39 +15065,44 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>Runs Monday to Friday year-round, plus Sundays in spring and summer, from Tofino's 1st Street Dock.</t>
+          <t>No service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>water-taxi:wt012</t>
+          <t>local-bus:vs-61</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Tofino Water Taxi</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>Tofino – Ahousaht (Flores Island)</t>
+          <t>61 Lumby/Vernon</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Alberni-Clayoquot (West Coast Vancouver Island)</t>
+          <t>Thompson Okanagan</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -14858,73 +15110,73 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Tofino</t>
+          <t>Lumby</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>Ahousaht (Flores Island)</t>
+          <t>Vernon</t>
         </is>
       </c>
       <c r="J255" t="b">
-        <v>0</v>
-      </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L255" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>Electric zero-emission vessel; year-round; an Ahousaht access fee applies.</t>
+          <t>Weekdays only.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>water-taxi:wt013</t>
+          <t>local-bus:vs-90</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Lasqueti Island Ferry (Western Pacific Marine)</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>French Creek – False Bay</t>
+          <t>90 UBCO/Vernon</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>qathet / Northern Gulf Islands</t>
+          <t>Southern Interior</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>daily</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>French Creek (Qualicum Beach)</t>
+          <t>Kelowna</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>Lasqueti Island</t>
+          <t>Vernon</t>
         </is>
       </c>
       <c r="J256" t="b">
@@ -14935,52 +15187,52 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
-        </is>
-      </c>
-      <c r="N256" t="inlineStr">
-        <is>
-          <t>Foot passengers and freight only, no cars; about an hour across, with no Tuesday sailings. Tickets sold on board.</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>water-taxi:wt014</t>
+          <t>local-bus:wct-1</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>West Coast Launch</t>
+          <t>West Coast Transit System (Tofino/Ucluelet)</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>Cow Bay (Prince Rupert) – Dodge Cove</t>
+          <t>1 Tofino / Ucluelet</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>North Coast</t>
+          <t>Vancouver Island</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>daily</t>
         </is>
       </c>
       <c r="G257" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Ucluelet</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Dodge Cove (Digby Island)</t>
+          <t>Tofino</t>
         </is>
       </c>
       <c r="J257" t="b">
@@ -14991,52 +15243,52 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="N257" t="inlineStr">
-        <is>
-          <t>Ferry-style service several days a week; the schedule varies by season.</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>water-taxi:wt015</t>
+          <t>local-bus:wk-10</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>West Coast Launch</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>Cow Bay (Prince Rupert) – Digby Island Airport</t>
+          <t>10 North Shore</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>North Coast</t>
+          <t>Kootenay Rockies</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G258" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Digby Island</t>
+          <t>Balfour</t>
         </is>
       </c>
       <c r="J258" t="b">
@@ -15047,52 +15299,57 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>About ten minutes across, timed with the airport shuttle; give advance notice.</t>
+          <t>No service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>water-taxi:wt016</t>
+          <t>local-bus:wk-10x</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>West Coast Launch</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>Cow Bay (Prince Rupert) – Metlakatla</t>
+          <t>10X North Shore Express</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>North Coast</t>
+          <t>Kootenay Rockies</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G259" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Metlakatla</t>
+          <t>Balfour</t>
         </is>
       </c>
       <c r="J259" t="b">
@@ -15103,39 +15360,44 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
         <is>
-          <t>About 30 minutes across; scheduled and charter service.</t>
+          <t>No service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>water-taxi:wt017</t>
+          <t>local-bus:wk-20</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>West Coast Launch</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>Cow Bay (Prince Rupert) – Oona River</t>
+          <t>20 Slocan Valley</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>North Coast</t>
+          <t>Kootenay Rockies</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -15143,73 +15405,73 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Slocan</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Oona River (Porcher Island)</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="J260" t="b">
-        <v>0</v>
-      </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L260" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>About an hour and a quarter to Porcher Island; call to arrange.</t>
+          <t>No service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>water-taxi:wt018</t>
+          <t>local-bus:wk-38</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Metlakatla Ferry Service</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>Prince Rupert (Cow Bay) – Metlakatla</t>
+          <t>38 Playmor via Pass Creek</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>North Coast</t>
+          <t>Kootenay Rockies</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G261" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Castlegar</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Brilliant</t>
         </is>
       </c>
       <c r="J261" t="b">
@@ -15220,39 +15482,44 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>Community ferry from Cow Bay, about 15 minutes across, with several departures Monday to Friday.</t>
+          <t>Runs Tuesday and Friday only.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>water-taxi:wt019</t>
+          <t>local-bus:wk-45</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>SeaCoastal Water Taxi (Kitasoo Xai'xais)</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>Bella Bella – Klemtu</t>
+          <t>45 Teck</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Central Coast (Great Bear Rainforest)</t>
+          <t>West Kootenay</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -15260,12 +15527,12 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Bella Bella</t>
+          <t>Rossland</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Klemtu</t>
+          <t>Trail</t>
         </is>
       </c>
       <c r="J262" t="b">
@@ -15276,39 +15543,39 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="N262" t="inlineStr">
-        <is>
-          <t>Scheduled run between Bella Bella and Klemtu; up to 12 passengers plus freight.</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>water-taxi:wt020</t>
+          <t>local-bus:wk-46</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Lund Water Taxi</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>Lund – Sarah Point (Sunshine Coast Trail)</t>
+          <t>46 Rossland</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>qathet (Powell River) / Sunshine Coast</t>
+          <t>West Kootenay</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -15316,60 +15583,55 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Lund</t>
+          <t>Trail</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Sarah Point (Malaspina Peninsula)</t>
+          <t>Rossland</t>
         </is>
       </c>
       <c r="J263" t="b">
-        <v>0</v>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L263" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="N263" t="inlineStr">
-        <is>
-          <t>By reservation; trailhead drop-off for the Sunshine Coast Trail (also Desolation Sound and Cortes).</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>water-taxi:wt021</t>
+          <t>local-bus:wk-52</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Cape Scott Water Taxi (North Coast Trail Shuttle)</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Port Hardy – Shushartie Bay</t>
+          <t>52 Nakusp-Playmor via Silverton</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Mount Waddington (North Vancouver Island)</t>
+          <t>Kootenay Rockies</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -15377,195 +15639,195 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Port Hardy</t>
+          <t>Nakusp</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Shushartie Bay (Cape Scott Park)</t>
+          <t>Slocan</t>
         </is>
       </c>
       <c r="J264" t="b">
-        <v>0</v>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L264" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>Pre-booked North Coast Trail drop-off, about an hour; 7am departures when booked; beach landings depend on the tide.</t>
+          <t>Wednesdays only.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>water-taxi:wt022</t>
+          <t>local-bus:wk-53</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Cape Scott Water Taxi (North Coast Trail Shuttle)</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>Port Hardy – Cape Sutil / Fisherman Bay</t>
+          <t>53 Nakusp-Edgewood</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Mount Waddington (North Vancouver Island)</t>
+          <t>Kootenay Rockies</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G265" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Port Hardy</t>
+          <t>Nakusp</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Fisherman Bay (Cape Scott Park)</t>
+          <t>Edgewood</t>
         </is>
       </c>
       <c r="J265" t="b">
-        <v>0</v>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L265" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>Pre-booked alternate North Coast Trail access; high-tide-only landings, 6-person minimum to Fisherman Bay.</t>
+          <t>Fridays only.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>water-taxi:wt023</t>
+          <t>local-bus:wk-58</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Cape Scott Water Taxi (North Coast Trail Shuttle)</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Port Hardy – Mid-Coast inlets</t>
+          <t>58 Kaslo-Argenta</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Mount Waddington / Central Coast</t>
+          <t>Kootenay Rockies</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>on-demand</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G266" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Port Hardy</t>
+          <t>Kaslo</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Calvert Island</t>
+          <t>Argenta</t>
         </is>
       </c>
       <c r="J266" t="b">
-        <v>0</v>
-      </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t>on demand only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L266" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>Thursdays only.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>water-taxi:wt024</t>
+          <t>local-bus:wk-72</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Qaya Way West Transportation</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Campbell River – Discovery Islands (Northern run)</t>
+          <t>72 Salmo-Nelson via Ymir</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Strathcona / Discovery Islands</t>
+          <t>Kootenay Rockies</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G267" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Campbell River</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Hemming Bay</t>
+          <t>Salmo</t>
         </is>
       </c>
       <c r="J267" t="b">
@@ -15576,207 +15838,222 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>Northern run Mondays and Fridays year-round, plus a seasonal Wednesday sailing; reservations required.</t>
+          <t>Runs Tuesday, Thursday and Friday only.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>water-taxi:wt025</t>
+          <t>local-bus:wk-74</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Discovery Launch Water Taxi</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>Campbell River – Discovery Islands &amp; Mainland Inlets</t>
+          <t>74 Nakusp-Nelson</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Strathcona / Discovery Islands</t>
+          <t>Kootenay Rockies</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G268" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Campbell River</t>
+          <t>Nakusp</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Bute Inlet (mainland)</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="J268" t="b">
-        <v>0</v>
-      </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L268" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>Runs Tuesday and Thursday only.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>water-taxi:wt026</t>
+          <t>local-bus:wk-76</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Blind Channel Water Taxi</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>Blind Channel (West Thurlow) – Outer Discovery Islands</t>
+          <t>76 Kaslo-Nelson</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Strathcona / Discovery Islands</t>
+          <t>Kootenay Rockies</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G269" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Blind Channel (West Thurlow Island)</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Quadra Island</t>
+          <t>Kaslo</t>
         </is>
       </c>
       <c r="J269" t="b">
-        <v>0</v>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L269" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>Runs Tuesday, Wednesday and Thursday only.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>water-taxi:wt027</t>
+          <t>local-bus:wk-98</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Discovery West Adventures</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>Campbell River – Outer Discovery Islands</t>
+          <t>98 Columbia Connector</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Strathcona / Discovery Islands</t>
+          <t>West Kootenay</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G270" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Campbell River</t>
+          <t>Castlegar</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Frederick Arm (mainland)</t>
+          <t>Trail</t>
         </is>
       </c>
       <c r="J270" t="b">
-        <v>0</v>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L270" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>water-taxi:wt028</t>
+          <t>local-bus:wk-99</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Sutil Charters</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Quadra Island – Cortes Island</t>
+          <t>99 Kootenay Connector</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Strathcona / Discovery Islands</t>
+          <t>West Kootenay</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -15784,340 +16061,315 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Quadra Island</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Cortes Island</t>
+          <t>Castlegar</t>
         </is>
       </c>
       <c r="J271" t="b">
-        <v>0</v>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L271" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>water-taxi:wt029</t>
+          <t>local-train:WCE</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>local-train</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Terracentric Coastal Adventures</t>
+          <t>TransLink (West Coast Express)</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Lund – Cortes Island</t>
+          <t>West Coast Express</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>qathet (Powell River) / Sunshine Coast</t>
+          <t>Metro Vancouver / Fraser Valley</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G272" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Lund</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Cortes Island</t>
+          <t>Mission</t>
         </is>
       </c>
       <c r="J272" t="b">
-        <v>0</v>
-      </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L272" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes, with conditions</t>
+        </is>
+      </c>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>Weekdays only, peak direction only: five trains toward Vancouver in the morning, five back in the evening.</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>water-taxi:wt030</t>
+          <t>rental:bud-cr-nan</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>rental-car</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Shorebird Expeditions</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>Tahsis – Yuquot (Friendly Cove)</t>
+          <t>One-way rental: Campbell River – Nanaimo</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Strathcona / West Coast Vancouver Island (Nootka Sound)</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="G273" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Tahsis</t>
+          <t>Campbell River</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Yuquot / Friendly Cove (Nootka Island)</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="J273" t="b">
-        <v>0</v>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L273" t="b">
         <v>0</v>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>water-taxi:wt031</t>
+          <t>rental:bud-nan-vic</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>rental-car</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Nootka Water Taxi</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>Gold River – Yuquot (Friendly Cove)</t>
+          <t>One-way rental: Nanaimo – Victoria</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Strathcona / West Coast Vancouver Island (Nootka Sound)</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="G274" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Gold River</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Hesquiat Peninsula</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="J274" t="b">
-        <v>0</v>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L274" t="b">
         <v>0</v>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>water-taxi:wt032</t>
+          <t>rental:bud-pa-nan</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>rental-car</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Zeballos Expeditions (Zeballos Water Taxi)</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>Zeballos – Nuchatlitz / Nootka Island</t>
+          <t>One-way rental: Port Alberni – Nanaimo</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Strathcona / West Coast Vancouver Island (Esperanza-Nootka)</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="G275" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Zeballos</t>
+          <t>Port Alberni</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Louie Bay (Nootka Island)</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="J275" t="b">
-        <v>0</v>
-      </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L275" t="b">
         <v>0</v>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>water-taxi:wt033</t>
+          <t>rental:bud-ph-nan</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>rental-car</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>West Coast Launch</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>Kitimat – Hartley Bay</t>
+          <t>One-way rental: Port Hardy – Nanaimo</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>North Coast / Kitimat-Stikine</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="G276" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Kitimat</t>
+          <t>Port Hardy</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Kemano</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="J276" t="b">
-        <v>0</v>
-      </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L276" t="b">
         <v>0</v>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="N276" t="inlineStr">
-        <is>
-          <t>About 1.5–2 hours down Douglas Channel; call to arrange.</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>water-taxi:wt034</t>
+          <t>rental:nat-cr-cx</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>rental-car</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>West Coast Launch</t>
+          <t>National Car &amp; Truck Rental (Vancouver Island)</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>Cow Bay (Prince Rupert) – Kitkatla (Gitxaała)</t>
+          <t>One-way rental: Campbell River – Comox</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>North Coast</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -16125,233 +16377,203 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Campbell River</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Kitkatla (Gitxaała)</t>
+          <t>Comox</t>
         </is>
       </c>
       <c r="J277" t="b">
         <v>1</v>
       </c>
       <c r="L277" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="N277" t="inlineStr">
-        <is>
-          <t>Twice-weekly ferry run in partnership with Gitxaała (Fridays 11am, Sundays noon); about 1.5–2 hours.</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>water-taxi:wt035</t>
+          <t>rental:nat-cr-nan</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>rental-car</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>West Coast Launch</t>
+          <t>National Car &amp; Truck Rental (Vancouver Island)</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>Cow Bay (Prince Rupert) – Lax Kw'alaams (Port Simpson)</t>
+          <t>One-way rental: Campbell River – Nanaimo</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>North Coast</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="G278" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Campbell River</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Ketchikan (Alaska, USA)</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="J278" t="b">
-        <v>0</v>
-      </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L278" t="b">
         <v>0</v>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="N278" t="inlineStr">
-        <is>
-          <t>Call to arrange; also serves Gingolx and the Khutzeymateen.</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>water-taxi:wt036</t>
+          <t>rental:nat-cr-ph</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>rental-car</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Tsimshian Storm (Kitkatla/Hartley Bay/Metlakatla)</t>
+          <t>National Car &amp; Truck Rental (Vancouver Island)</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>Prince Rupert (Metlakatla dock) – Kitkatla</t>
+          <t>One-way rental: Campbell River – Port Hardy</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>North Coast</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="G279" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Campbell River</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Kitkatla (Gitxaała)</t>
+          <t>Port Hardy</t>
         </is>
       </c>
       <c r="J279" t="b">
         <v>1</v>
       </c>
       <c r="L279" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="N279" t="inlineStr">
-        <is>
-          <t>Departs Prince Rupert twice weekly at 10am, returning from Kitkatla at noon; sailings are weather-dependent.</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>water-taxi:wt037</t>
+          <t>rental:nat-cx-nan</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>rental-car</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>SeaCoastal Water Taxi (Kitasoo Xai'xais)</t>
+          <t>National Car &amp; Truck Rental (Vancouver Island)</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>Klemtu / Bella Bella – Central Coast communities</t>
+          <t>One-way rental: Comox – Nanaimo</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Central Coast (Great Bear Rainforest)</t>
-        </is>
-      </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>on-demand</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="G280" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Klemtu</t>
+          <t>Comox</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="J280" t="b">
-        <v>0</v>
-      </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>on demand only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L280" t="b">
         <v>0</v>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>water-taxi:wt038</t>
+          <t>rental:nat-cx-ph</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>rental-car</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>MV Uchuck III (Nootka Sound Service Ltd / Get West)</t>
+          <t>National Car &amp; Truck Rental (Vancouver Island)</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Gold River – Tahsis</t>
+          <t>One-way rental: Comox – Port Hardy</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Strathcona / West Coast Vancouver Island (Nootka Sound)</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -16359,55 +16581,50 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Gold River</t>
+          <t>Comox</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>Tahsis</t>
+          <t>Port Hardy</t>
         </is>
       </c>
       <c r="J281" t="b">
         <v>1</v>
       </c>
       <c r="L281" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="N281" t="inlineStr">
-        <is>
-          <t>A working coastal freighter that takes passengers; Nootka Sound day trips most Tuesdays.</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>water-taxi:wt039</t>
+          <t>rental:nat-nan-vic</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>rental-car</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>MV Uchuck III (Nootka Sound Service Ltd / Get West)</t>
+          <t>National Car &amp; Truck Rental (Vancouver Island)</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>Gold River – Yuquot (Friendly Cove)</t>
+          <t>One-way rental: Nanaimo – Victoria</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Strathcona / West Coast Vancouver Island (Nootka Sound)</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -16415,82 +16632,2691 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Gold River</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Yuquot / Friendly Cove (Nootka Island)</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="J282" t="b">
         <v>1</v>
       </c>
       <c r="L282" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="N282" t="inlineStr">
-        <is>
-          <t>Wednesday and Saturday sailings pick up Nootka Trail hikers at Friendly Cove, late June to early September.</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
+          <t>rental:nat-ph-nan</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>rental-car</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>National Car &amp; Truck Rental (Vancouver Island)</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>One-way rental: Port Hardy – Nanaimo</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Vancouver Island</t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>2</v>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>Port Hardy</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Nanaimo</t>
+        </is>
+      </c>
+      <c r="J283" t="b">
+        <v>1</v>
+      </c>
+      <c r="L283" t="b">
+        <v>0</v>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>yes, with conditions</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>skytrain:1</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>skytrain</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>TransLink</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>SkyTrain (all lines)</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Metro Vancouver</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G284" t="n">
+        <v>54</v>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="J284" t="b">
+        <v>1</v>
+      </c>
+      <c r="L284" t="b">
+        <v>1</v>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>yes, with conditions</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>train:amtrak-cascades</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>intercity-train</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Amtrak Cascades</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Vancouver – Seattle (Cascades)</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>cross-border</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G285" t="n">
+        <v>2</v>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>Vancouver Pacific Central</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Seattle Downtown WA</t>
+        </is>
+      </c>
+      <c r="J285" t="b">
+        <v>1</v>
+      </c>
+      <c r="L285" t="b">
+        <v>1</v>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>yes, with conditions</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>Two daily round trips from Pacific Central; reserve bike space when you book. Passport required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>train:via-canadian</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>intercity-train</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>VIA Rail</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>The Canadian (Vancouver – Kamloops North – Jasper)</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>southwest</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
+      <c r="G286" t="n">
+        <v>3</v>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>Vancouver Pacific Central</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Jasper AB</t>
+        </is>
+      </c>
+      <c r="J286" t="b">
+        <v>1</v>
+      </c>
+      <c r="L286" t="b">
+        <v>1</v>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>yes, with conditions</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>Two departures a week in season; bikes can be checked on and off at Vancouver and Jasper only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>train:via-skeena</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>intercity-train</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>VIA Rail</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Skeena (Prince Rupert – Prince George – Jasper)</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>north</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
+      <c r="G287" t="n">
+        <v>10</v>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>Prince Rupert</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Jasper AB</t>
+        </is>
+      </c>
+      <c r="J287" t="b">
+        <v>1</v>
+      </c>
+      <c r="L287" t="b">
+        <v>1</v>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>yes, with conditions</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>Three departures a week; the trip includes an overnight stop in Prince George (book your own hotel).</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>water-taxi:wt001</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Victoria Harbour Ferry</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Empress Dock – Fisherman's Wharf</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Capital (Greater Victoria)</t>
+        </is>
+      </c>
+      <c r="G288" t="n">
+        <v>4</v>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Esquimalt</t>
+        </is>
+      </c>
+      <c r="J288" t="b">
+        <v>0</v>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L288" t="b">
+        <v>0</v>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>water-taxi:wt002</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Victoria Harbour Ferry</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Empress Dock – Selkirk Landing (Gorge)</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Capital (Greater Victoria)</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>3</v>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Victoria (Victoria West)</t>
+        </is>
+      </c>
+      <c r="J289" t="b">
+        <v>0</v>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L289" t="b">
+        <v>0</v>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>water-taxi:wt003</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>BLAST (English Bay Launch)</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Snug Cove – Coal Harbour</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Metro Vancouver / Howe Sound</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>2</v>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>Bowen Island</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="J290" t="b">
+        <v>0</v>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>no longer operating</t>
+        </is>
+      </c>
+      <c r="L290" t="b">
+        <v>0</v>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>Weekday commuter water taxi, by reservation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>water-taxi:wt004</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>BLAST (English Bay Launch)</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Snug Cove – Granville Island</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Metro Vancouver / Howe Sound</t>
+        </is>
+      </c>
+      <c r="G291" t="n">
+        <v>2</v>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>Bowen Island</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
+      </c>
+      <c r="J291" t="b">
+        <v>0</v>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>no longer operating</t>
+        </is>
+      </c>
+      <c r="L291" t="b">
+        <v>0</v>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>Summer-weekend service to Granville Island.</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>water-taxi:wt005</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Cormorant Marine Water Taxi</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Horseshoe Bay – Snug Cove</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Metro Vancouver / Howe Sound</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>on-demand</t>
+        </is>
+      </c>
+      <c r="G292" t="n">
+        <v>2</v>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>West Vancouver</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Bowen Island</t>
+        </is>
+      </c>
+      <c r="J292" t="b">
+        <v>0</v>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L292" t="b">
+        <v>0</v>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>water-taxi:wt006</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Cormorant Marine Water Taxi</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Horseshoe Bay – Gambier Harbour</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Metro Vancouver / Howe Sound</t>
+        </is>
+      </c>
+      <c r="G293" t="n">
+        <v>2</v>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>West Vancouver</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Gambier Island</t>
+        </is>
+      </c>
+      <c r="J293" t="b">
+        <v>0</v>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L293" t="b">
+        <v>0</v>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>water-taxi:wt007</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Lund Water Taxi</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Lund – Savary Island</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>qathet (Powell River) / Sunshine Coast</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G294" t="n">
+        <v>2</v>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Savary Island</t>
+        </is>
+      </c>
+      <c r="J294" t="b">
+        <v>1</v>
+      </c>
+      <c r="L294" t="b">
+        <v>1</v>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>Year-round walk-on service, near-hourly in July and August; reservations required. E-bikes not carried (barge by arrangement).</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>water-taxi:wt008</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Savary Island Ferry (Finn Bay Marine / Access Point Marine)</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Lund – Savary Island</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>qathet (Powell River) / Sunshine Coast</t>
+        </is>
+      </c>
+      <c r="G295" t="n">
+        <v>2</v>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Savary Island</t>
+        </is>
+      </c>
+      <c r="J295" t="b">
+        <v>0</v>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>no longer operating</t>
+        </is>
+      </c>
+      <c r="L295" t="b">
+        <v>0</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>Departures about every 30 minutes, June to September, from behind the Lund Hotel; reservations required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>water-taxi:wt009</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Discovery Launch Water Taxi</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Campbell River – Cortes Island</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Strathcona / Discovery Islands</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
+      <c r="G296" t="n">
+        <v>2</v>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>Campbell River</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Cortes Island</t>
+        </is>
+      </c>
+      <c r="J296" t="b">
+        <v>1</v>
+      </c>
+      <c r="L296" t="b">
+        <v>1</v>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>Scheduled Fridays and Sundays in summer (also calls at Savary, Hernando and Lund); otherwise by charter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>water-taxi:wt010</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Qaya Way West Transportation</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Campbell River – Savary Island</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Strathcona / Discovery Islands</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>seasonal-varies</t>
+        </is>
+      </c>
+      <c r="G297" t="n">
+        <v>4</v>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>Campbell River</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Savary Island</t>
+        </is>
+      </c>
+      <c r="J297" t="b">
+        <v>1</v>
+      </c>
+      <c r="L297" t="b">
+        <v>1</v>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>Southern run daily June 26 to September 7, calling at Manson's Landing and Hernando; reservations required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>water-taxi:wt011</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Ahous Hakuum (MHSS)</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Tofino – Maaqutusiis (Ahousaht)</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Alberni-Clayoquot (West Coast Vancouver Island)</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
+      <c r="G298" t="n">
+        <v>2</v>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>Tofino</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Ahousaht (Flores Island)</t>
+        </is>
+      </c>
+      <c r="J298" t="b">
+        <v>1</v>
+      </c>
+      <c r="L298" t="b">
+        <v>1</v>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>Runs Monday to Friday year-round, plus Sundays in spring and summer, from Tofino's 1st Street Dock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>water-taxi:wt012</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Tofino Water Taxi</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Tofino – Ahousaht (Flores Island)</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Alberni-Clayoquot (West Coast Vancouver Island)</t>
+        </is>
+      </c>
+      <c r="G299" t="n">
+        <v>2</v>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>Tofino</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Ahousaht (Flores Island)</t>
+        </is>
+      </c>
+      <c r="J299" t="b">
+        <v>0</v>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L299" t="b">
+        <v>0</v>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>Electric zero-emission vessel; year-round; an Ahousaht access fee applies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>water-taxi:wt013</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Lasqueti Island Ferry (Western Pacific Marine)</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>French Creek – False Bay</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>qathet / Northern Gulf Islands</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G300" t="n">
+        <v>2</v>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>French Creek (Qualicum Beach)</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Lasqueti Island</t>
+        </is>
+      </c>
+      <c r="J300" t="b">
+        <v>1</v>
+      </c>
+      <c r="L300" t="b">
+        <v>1</v>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>yes, with conditions</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>Foot passengers and freight only, no cars; about an hour across, with no Tuesday sailings. Tickets sold on board.</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>water-taxi:wt014</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>West Coast Launch</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Cow Bay (Prince Rupert) – Dodge Cove</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>North Coast</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
+      <c r="G301" t="n">
+        <v>2</v>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>Prince Rupert</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Dodge Cove (Digby Island)</t>
+        </is>
+      </c>
+      <c r="J301" t="b">
+        <v>1</v>
+      </c>
+      <c r="L301" t="b">
+        <v>1</v>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>Ferry-style service several days a week; the schedule varies by season.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>water-taxi:wt015</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>West Coast Launch</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Cow Bay (Prince Rupert) – Digby Island Airport</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>North Coast</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
+      <c r="G302" t="n">
+        <v>2</v>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>Prince Rupert</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Digby Island</t>
+        </is>
+      </c>
+      <c r="J302" t="b">
+        <v>1</v>
+      </c>
+      <c r="L302" t="b">
+        <v>1</v>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>About ten minutes across, timed with the airport shuttle; give advance notice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>water-taxi:wt016</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>West Coast Launch</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Cow Bay (Prince Rupert) – Metlakatla</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>North Coast</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
+      <c r="G303" t="n">
+        <v>2</v>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>Prince Rupert</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Metlakatla</t>
+        </is>
+      </c>
+      <c r="J303" t="b">
+        <v>1</v>
+      </c>
+      <c r="L303" t="b">
+        <v>1</v>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>About 30 minutes across; scheduled and charter service.</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>water-taxi:wt017</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>West Coast Launch</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Cow Bay (Prince Rupert) – Oona River</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>North Coast</t>
+        </is>
+      </c>
+      <c r="G304" t="n">
+        <v>2</v>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>Prince Rupert</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Oona River (Porcher Island)</t>
+        </is>
+      </c>
+      <c r="J304" t="b">
+        <v>0</v>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L304" t="b">
+        <v>0</v>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>About an hour and a quarter to Porcher Island; call to arrange.</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>water-taxi:wt018</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Metlakatla Ferry Service</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Prince Rupert (Cow Bay) – Metlakatla</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>North Coast</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
+      <c r="G305" t="n">
+        <v>1</v>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>Prince Rupert</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Prince Rupert</t>
+        </is>
+      </c>
+      <c r="J305" t="b">
+        <v>1</v>
+      </c>
+      <c r="L305" t="b">
+        <v>1</v>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>Community ferry from Cow Bay, about 15 minutes across, with several departures Monday to Friday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>water-taxi:wt019</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>SeaCoastal Water Taxi (Kitasoo Xai'xais)</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Bella Bella – Klemtu</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Central Coast (Great Bear Rainforest)</t>
+        </is>
+      </c>
+      <c r="G306" t="n">
+        <v>2</v>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>Bella Bella</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>Klemtu</t>
+        </is>
+      </c>
+      <c r="J306" t="b">
+        <v>1</v>
+      </c>
+      <c r="L306" t="b">
+        <v>1</v>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>Scheduled run between Bella Bella and Klemtu; up to 12 passengers plus freight.</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>water-taxi:wt020</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Lund Water Taxi</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Lund – Sarah Point (Sunshine Coast Trail)</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>qathet (Powell River) / Sunshine Coast</t>
+        </is>
+      </c>
+      <c r="G307" t="n">
+        <v>2</v>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Sarah Point (Malaspina Peninsula)</t>
+        </is>
+      </c>
+      <c r="J307" t="b">
+        <v>0</v>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L307" t="b">
+        <v>0</v>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>By reservation; trailhead drop-off for the Sunshine Coast Trail (also Desolation Sound and Cortes).</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>water-taxi:wt021</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Cape Scott Water Taxi (North Coast Trail Shuttle)</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Port Hardy – Shushartie Bay</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Mount Waddington (North Vancouver Island)</t>
+        </is>
+      </c>
+      <c r="G308" t="n">
+        <v>2</v>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>Port Hardy</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>Shushartie Bay (Cape Scott Park)</t>
+        </is>
+      </c>
+      <c r="J308" t="b">
+        <v>0</v>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L308" t="b">
+        <v>0</v>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>Pre-booked North Coast Trail drop-off, about an hour; 7am departures when booked; beach landings depend on the tide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>water-taxi:wt022</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Cape Scott Water Taxi (North Coast Trail Shuttle)</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Port Hardy – Cape Sutil / Fisherman Bay</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Mount Waddington (North Vancouver Island)</t>
+        </is>
+      </c>
+      <c r="G309" t="n">
+        <v>3</v>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>Port Hardy</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Fisherman Bay (Cape Scott Park)</t>
+        </is>
+      </c>
+      <c r="J309" t="b">
+        <v>0</v>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L309" t="b">
+        <v>0</v>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>Pre-booked alternate North Coast Trail access; high-tide-only landings, 6-person minimum to Fisherman Bay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>water-taxi:wt023</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Cape Scott Water Taxi (North Coast Trail Shuttle)</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Port Hardy – Mid-Coast inlets</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Mount Waddington / Central Coast</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>on-demand</t>
+        </is>
+      </c>
+      <c r="G310" t="n">
+        <v>7</v>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>Port Hardy</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>Calvert Island</t>
+        </is>
+      </c>
+      <c r="J310" t="b">
+        <v>0</v>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>on demand only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L310" t="b">
+        <v>0</v>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>water-taxi:wt024</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Qaya Way West Transportation</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Campbell River – Discovery Islands (Northern run)</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Strathcona / Discovery Islands</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
+      <c r="G311" t="n">
+        <v>10</v>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>Campbell River</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>Hemming Bay</t>
+        </is>
+      </c>
+      <c r="J311" t="b">
+        <v>1</v>
+      </c>
+      <c r="L311" t="b">
+        <v>1</v>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>Northern run Mondays and Fridays year-round, plus a seasonal Wednesday sailing; reservations required.</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>water-taxi:wt025</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Discovery Launch Water Taxi</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Campbell River – Discovery Islands &amp; Mainland Inlets</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Strathcona / Discovery Islands</t>
+        </is>
+      </c>
+      <c r="G312" t="n">
+        <v>6</v>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>Campbell River</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Bute Inlet (mainland)</t>
+        </is>
+      </c>
+      <c r="J312" t="b">
+        <v>0</v>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L312" t="b">
+        <v>0</v>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>water-taxi:wt026</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Blind Channel Water Taxi</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Blind Channel (West Thurlow) – Outer Discovery Islands</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Strathcona / Discovery Islands</t>
+        </is>
+      </c>
+      <c r="G313" t="n">
+        <v>5</v>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>Blind Channel (West Thurlow Island)</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Quadra Island</t>
+        </is>
+      </c>
+      <c r="J313" t="b">
+        <v>0</v>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L313" t="b">
+        <v>0</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>water-taxi:wt027</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Discovery West Adventures</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Campbell River – Outer Discovery Islands</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Strathcona / Discovery Islands</t>
+        </is>
+      </c>
+      <c r="G314" t="n">
+        <v>4</v>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>Campbell River</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Frederick Arm (mainland)</t>
+        </is>
+      </c>
+      <c r="J314" t="b">
+        <v>0</v>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L314" t="b">
+        <v>0</v>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>water-taxi:wt028</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Sutil Charters</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Quadra Island – Cortes Island</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Strathcona / Discovery Islands</t>
+        </is>
+      </c>
+      <c r="G315" t="n">
+        <v>2</v>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>Quadra Island</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Cortes Island</t>
+        </is>
+      </c>
+      <c r="J315" t="b">
+        <v>0</v>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L315" t="b">
+        <v>0</v>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>water-taxi:wt029</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Terracentric Coastal Adventures</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Lund – Cortes Island</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>qathet (Powell River) / Sunshine Coast</t>
+        </is>
+      </c>
+      <c r="G316" t="n">
+        <v>2</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Cortes Island</t>
+        </is>
+      </c>
+      <c r="J316" t="b">
+        <v>0</v>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L316" t="b">
+        <v>0</v>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>water-taxi:wt030</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Shorebird Expeditions</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Tahsis – Yuquot (Friendly Cove)</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Strathcona / West Coast Vancouver Island (Nootka Sound)</t>
+        </is>
+      </c>
+      <c r="G317" t="n">
+        <v>3</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>Tahsis</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Yuquot / Friendly Cove (Nootka Island)</t>
+        </is>
+      </c>
+      <c r="J317" t="b">
+        <v>0</v>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L317" t="b">
+        <v>0</v>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>water-taxi:wt031</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Nootka Water Taxi</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Gold River – Yuquot (Friendly Cove)</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Strathcona / West Coast Vancouver Island (Nootka Sound)</t>
+        </is>
+      </c>
+      <c r="G318" t="n">
+        <v>3</v>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>Gold River</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Hesquiat Peninsula</t>
+        </is>
+      </c>
+      <c r="J318" t="b">
+        <v>0</v>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L318" t="b">
+        <v>0</v>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>water-taxi:wt032</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Zeballos Expeditions (Zeballos Water Taxi)</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Zeballos – Nuchatlitz / Nootka Island</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Strathcona / West Coast Vancouver Island (Esperanza-Nootka)</t>
+        </is>
+      </c>
+      <c r="G319" t="n">
+        <v>5</v>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>Zeballos</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Louie Bay (Nootka Island)</t>
+        </is>
+      </c>
+      <c r="J319" t="b">
+        <v>0</v>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L319" t="b">
+        <v>0</v>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>water-taxi:wt033</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>West Coast Launch</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Kitimat – Hartley Bay</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>North Coast / Kitimat-Stikine</t>
+        </is>
+      </c>
+      <c r="G320" t="n">
+        <v>3</v>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>Kitimat</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Kemano</t>
+        </is>
+      </c>
+      <c r="J320" t="b">
+        <v>0</v>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L320" t="b">
+        <v>0</v>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>About 1.5–2 hours down Douglas Channel; call to arrange.</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>water-taxi:wt034</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>West Coast Launch</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Cow Bay (Prince Rupert) – Kitkatla (Gitxaała)</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>North Coast</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
+      <c r="G321" t="n">
+        <v>2</v>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>Prince Rupert</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Kitkatla (Gitxaała)</t>
+        </is>
+      </c>
+      <c r="J321" t="b">
+        <v>1</v>
+      </c>
+      <c r="L321" t="b">
+        <v>1</v>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>Twice-weekly ferry run in partnership with Gitxaała (Fridays 11am, Sundays noon); about 1.5–2 hours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>water-taxi:wt035</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>West Coast Launch</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Cow Bay (Prince Rupert) – Lax Kw'alaams (Port Simpson)</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>North Coast</t>
+        </is>
+      </c>
+      <c r="G322" t="n">
+        <v>5</v>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>Prince Rupert</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Ketchikan (Alaska, USA)</t>
+        </is>
+      </c>
+      <c r="J322" t="b">
+        <v>0</v>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L322" t="b">
+        <v>0</v>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>Call to arrange; also serves Gingolx and the Khutzeymateen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>water-taxi:wt036</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Tsimshian Storm (Kitkatla/Hartley Bay/Metlakatla)</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Prince Rupert (Metlakatla dock) – Kitkatla</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>North Coast</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
+      <c r="G323" t="n">
+        <v>4</v>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>Prince Rupert</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Kitkatla (Gitxaała)</t>
+        </is>
+      </c>
+      <c r="J323" t="b">
+        <v>1</v>
+      </c>
+      <c r="L323" t="b">
+        <v>1</v>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>Departs Prince Rupert twice weekly at 10am, returning from Kitkatla at noon; sailings are weather-dependent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>water-taxi:wt037</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>SeaCoastal Water Taxi (Kitasoo Xai'xais)</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Klemtu / Bella Bella – Central Coast communities</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Central Coast (Great Bear Rainforest)</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>on-demand</t>
+        </is>
+      </c>
+      <c r="G324" t="n">
+        <v>7</v>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>Klemtu</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Prince Rupert</t>
+        </is>
+      </c>
+      <c r="J324" t="b">
+        <v>0</v>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>on demand only, not a scheduled service</t>
+        </is>
+      </c>
+      <c r="L324" t="b">
+        <v>0</v>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>water-taxi:wt038</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>MV Uchuck III (Nootka Sound Service Ltd / Get West)</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Gold River – Tahsis</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Strathcona / West Coast Vancouver Island (Nootka Sound)</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
+      <c r="G325" t="n">
+        <v>2</v>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>Gold River</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Tahsis</t>
+        </is>
+      </c>
+      <c r="J325" t="b">
+        <v>1</v>
+      </c>
+      <c r="L325" t="b">
+        <v>1</v>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>A working coastal freighter that takes passengers; Nootka Sound day trips most Tuesdays.</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>water-taxi:wt039</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>MV Uchuck III (Nootka Sound Service Ltd / Get West)</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Gold River – Yuquot (Friendly Cove)</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Strathcona / West Coast Vancouver Island (Nootka Sound)</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
+      <c r="G326" t="n">
+        <v>2</v>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>Gold River</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Yuquot / Friendly Cove (Nootka Island)</t>
+        </is>
+      </c>
+      <c r="J326" t="b">
+        <v>1</v>
+      </c>
+      <c r="L326" t="b">
+        <v>1</v>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>Wednesday and Saturday sailings pick up Nootka Trail hikers at Friendly Cove, late June to early September.</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
           <t>water-taxi:wt040</t>
         </is>
       </c>
-      <c r="B283" t="inlineStr">
+      <c r="B327" t="inlineStr">
         <is>
           <t>water-taxi</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr">
+      <c r="C327" t="inlineStr">
         <is>
           <t>MV Uchuck III (Nootka Sound Service Ltd / Get West)</t>
         </is>
       </c>
-      <c r="D283" t="inlineStr">
+      <c r="D327" t="inlineStr">
         <is>
           <t>Gold River – Kyuquot</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
+      <c r="E327" t="inlineStr">
         <is>
           <t>Strathcona / West Coast Vancouver Island (Nootka–Kyuquot)</t>
         </is>
       </c>
-      <c r="G283" t="n">
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
+      <c r="G327" t="n">
         <v>4</v>
       </c>
-      <c r="H283" t="inlineStr">
+      <c r="H327" t="inlineStr">
         <is>
           <t>Gold River</t>
         </is>
       </c>
-      <c r="I283" t="inlineStr">
+      <c r="I327" t="inlineStr">
         <is>
           <t>Kyuquot</t>
         </is>
       </c>
-      <c r="J283" t="b">
-        <v>1</v>
-      </c>
-      <c r="L283" t="b">
-        <v>1</v>
-      </c>
-      <c r="M283" t="inlineStr">
+      <c r="J327" t="b">
+        <v>1</v>
+      </c>
+      <c r="L327" t="b">
+        <v>1</v>
+      </c>
+      <c r="M327" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="N283" t="inlineStr">
+      <c r="N327" t="inlineStr">
         <is>
           <t>Overnight run to Kyuquot via Esperanza Inlet, Thursday to Friday, June to September.</t>
         </is>

--- a/research/files/bc_transit_routes.xlsx
+++ b/research/files/bc_transit_routes.xlsx
@@ -513,7 +513,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Routes: 326 rows, 14 columns.</t>
+          <t>Routes: 327 rows, 14 columns.</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Of the 326 routes, 267 are part of the network we route journeys across. The rest are published too, each with the reason we set it aside, because what was excluded is part of the picture.</t>
+          <t>Of the 327 routes, 268 are part of the network we route journeys across. The rest are published too, each with the reason we set it aside, because what was excluded is part of the picture.</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N327"/>
+  <dimension ref="A1:N328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,7 +10651,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>local-bus:cvt-34</t>
+          <t>local-bus:cv-2</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -10666,7 +10666,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>34 Ladysmith-Chemainus</t>
+          <t>2 Cumberland / Anfield Centre</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -10684,12 +10684,12 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Ladysmith</t>
+          <t>Cumberland</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>North Cowichan</t>
+          <t>Courtenay</t>
         </is>
       </c>
       <c r="J179" t="b">
@@ -10707,7 +10707,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>local-bus:cvt-36</t>
+          <t>local-bus:cvt-34</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>36 Ladysmith-Duncan Express</t>
+          <t>34 Ladysmith-Chemainus</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10736,7 +10736,7 @@
         </is>
       </c>
       <c r="G180" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H180" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Duncan</t>
+          <t>North Cowichan</t>
         </is>
       </c>
       <c r="J180" t="b">
@@ -10763,7 +10763,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>local-bus:cvt-6</t>
+          <t>local-bus:cvt-36</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>6 Crofton-Chemainus</t>
+          <t>36 Ladysmith-Duncan Express</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10788,15 +10788,15 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G181" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>North Cowichan</t>
+          <t>Ladysmith</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -10819,7 +10819,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>local-bus:cvt-66</t>
+          <t>local-bus:cvt-6</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>66 CVX Cowichan - Victoria Express</t>
+          <t>6 Crofton-Chemainus</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10848,16 +10848,16 @@
         </is>
       </c>
       <c r="G182" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H182" t="inlineStr">
         <is>
+          <t>North Cowichan</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
           <t>Duncan</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>North Cowichan</t>
         </is>
       </c>
       <c r="J182" t="b">
@@ -10875,7 +10875,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>local-bus:cvt-7</t>
+          <t>local-bus:cvt-66</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>7 Cowichan Lake</t>
+          <t>66 CVX Cowichan - Victoria Express</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10904,7 +10904,7 @@
         </is>
       </c>
       <c r="G183" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H183" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>Lake Cowichan</t>
+          <t>North Cowichan</t>
         </is>
       </c>
       <c r="J183" t="b">
@@ -10931,7 +10931,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>local-bus:cvt-8</t>
+          <t>local-bus:cvt-7</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>8 Mill Bay via Telegraph Rd/Duncan via Shawnigan Lk</t>
+          <t>7 Cowichan Lake</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Mill Bay</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Duncan</t>
+          <t>Lake Cowichan</t>
         </is>
       </c>
       <c r="J184" t="b">
@@ -10987,7 +10987,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>local-bus:cvt-9</t>
+          <t>local-bus:cvt-8</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11002,7 +11002,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>9 Mill Bay via Shawnigan Lk/Duncan via Telegraph Rd</t>
+          <t>8 Mill Bay via Telegraph Rd/Duncan via Shawnigan Lk</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
+          <t>Mill Bay</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
           <t>Duncan</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Mill Bay</t>
         </is>
       </c>
       <c r="J185" t="b">
@@ -11043,7 +11043,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>local-bus:cvt-99</t>
+          <t>local-bus:cvt-9</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>99 SVX Shawnigan Lake - Victoria Express</t>
+          <t>9 Mill Bay via Shawnigan Lk/Duncan via Telegraph Rd</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11068,20 +11068,20 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G186" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Cobble Hill</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Mill Bay</t>
         </is>
       </c>
       <c r="J186" t="b">
@@ -11093,18 +11093,13 @@
       <c r="M186" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>Weekdays only.</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>local-bus:ea-goose</t>
+          <t>local-bus:cvt-99</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11114,12 +11109,12 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Electric Alpine Biking</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Galloping Goose Trail shuttle</t>
+          <t>99 SVX Shawnigan Lake - Victoria Express</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -11129,20 +11124,20 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>on-demand</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G187" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>View Royal</t>
+          <t>Cobble Hill</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Sooke</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="J187" t="b">
@@ -11153,14 +11148,19 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Weekdays only.</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>local-bus:ek-22</t>
+          <t>local-bus:ea-goose</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11170,35 +11170,35 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>BC Transit</t>
+          <t>Electric Alpine Biking</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>22 KC Commuter</t>
+          <t>Galloping Goose Trail shuttle</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Kootenay</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>on-demand</t>
         </is>
       </c>
       <c r="G188" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Cranbrook</t>
+          <t>View Royal</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Kimberley</t>
+          <t>Sooke</t>
         </is>
       </c>
       <c r="J188" t="b">
@@ -11209,14 +11209,14 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>local-bus:ek-31</t>
+          <t>local-bus:ek-22</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>31 South Connector</t>
+          <t>22 KC Commuter</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Kootenay Rockies</t>
+          <t>Kootenay</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -11249,12 +11249,12 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Invermere</t>
+          <t>Cranbrook</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Canal Flats</t>
+          <t>Kimberley</t>
         </is>
       </c>
       <c r="J189" t="b">
@@ -11266,18 +11266,13 @@
       <c r="M189" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N189" t="inlineStr">
-        <is>
-          <t>Weekdays only.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>local-bus:ek-32</t>
+          <t>local-bus:ek-31</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -11292,7 +11287,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>32 North Connector</t>
+          <t>31 South Connector</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11315,7 +11310,7 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Edgewater</t>
+          <t>Canal Flats</t>
         </is>
       </c>
       <c r="J190" t="b">
@@ -11338,7 +11333,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>local-bus:ek-41</t>
+          <t>local-bus:ek-32</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -11353,7 +11348,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>41 Fernie / Sparwood / Elkford</t>
+          <t>32 North Connector</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11367,16 +11362,16 @@
         </is>
       </c>
       <c r="G191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Elkford</t>
+          <t>Invermere</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Fernie</t>
+          <t>Edgewater</t>
         </is>
       </c>
       <c r="J191" t="b">
@@ -11399,7 +11394,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>local-bus:fv-21</t>
+          <t>local-bus:ek-41</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -11414,30 +11409,30 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>21 Fraser Hwy</t>
+          <t>41 Fernie / Sparwood / Elkford</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Metro Vancouver / Fraser Valley</t>
+          <t>Kootenay Rockies</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G192" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Langley</t>
+          <t>Elkford</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Abbotsford</t>
+          <t>Fernie</t>
         </is>
       </c>
       <c r="J192" t="b">
@@ -11449,13 +11444,18 @@
       <c r="M192" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Weekdays only.</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>local-bus:fv-21a</t>
+          <t>local-bus:fv-21</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -11470,7 +11470,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>21A Fraser Hwy</t>
+          <t>21 Fraser Hwy</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -11511,7 +11511,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>local-bus:fv-31</t>
+          <t>local-bus:fv-21a</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>31 Valley Connector</t>
+          <t>21A Fraser Hwy</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -11544,7 +11544,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Mission</t>
+          <t>Langley</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -11567,7 +11567,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>local-bus:fv-31a</t>
+          <t>local-bus:fv-31</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -11582,7 +11582,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>31A Valley Connector</t>
+          <t>31 Valley Connector</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11623,7 +11623,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>local-bus:fv-31x</t>
+          <t>local-bus:fv-31a</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -11638,7 +11638,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>31X Valley Connector</t>
+          <t>31A Valley Connector</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -11656,12 +11656,12 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
+          <t>Mission</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
           <t>Abbotsford</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>Mission</t>
         </is>
       </c>
       <c r="J196" t="b">
@@ -11679,7 +11679,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>local-bus:fv-55</t>
+          <t>local-bus:fv-31x</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>55 Yarrow - Greendale</t>
+          <t>31X Valley Connector</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -11712,12 +11712,12 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Chilliwack</t>
+          <t>Abbotsford</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Abbotsford</t>
+          <t>Mission</t>
         </is>
       </c>
       <c r="J197" t="b">
@@ -11735,7 +11735,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>local-bus:fv-66</t>
+          <t>local-bus:fv-55</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>66 Fraser Valley Express</t>
+          <t>55 Yarrow - Greendale</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -11760,11 +11760,11 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G198" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Burnaby</t>
+          <t>Abbotsford</t>
         </is>
       </c>
       <c r="J198" t="b">
@@ -11791,7 +11791,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>local-bus:fv-71</t>
+          <t>local-bus:fv-66</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>71 Agassiz-Harrison</t>
+          <t>66 Fraser Valley Express</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -11820,16 +11820,16 @@
         </is>
       </c>
       <c r="G199" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Harrison Hot Springs</t>
+          <t>Chilliwack</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Chilliwack</t>
+          <t>Burnaby</t>
         </is>
       </c>
       <c r="J199" t="b">
@@ -11847,7 +11847,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>local-bus:fv-72</t>
+          <t>local-bus:fv-71</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -11862,17 +11862,17 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>72 Hope</t>
+          <t>71 Agassiz-Harrison</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Vancouver, Coast &amp; Mountains</t>
+          <t>Metro Vancouver / Fraser Valley</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -11880,12 +11880,12 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Hope</t>
+          <t>Harrison Hot Springs</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Kent</t>
+          <t>Chilliwack</t>
         </is>
       </c>
       <c r="J200" t="b">
@@ -11897,18 +11897,13 @@
       <c r="M200" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr">
-        <is>
-          <t>No service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>local-bus:krt-23</t>
+          <t>local-bus:fv-72</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -11923,17 +11918,17 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>23 Lake Country</t>
+          <t>72 Hope</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Southern Interior</t>
+          <t>Vancouver, Coast &amp; Mountains</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -11941,12 +11936,12 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Kelowna</t>
+          <t>Hope</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Kelowna</t>
+          <t>Kent</t>
         </is>
       </c>
       <c r="J201" t="b">
@@ -11962,14 +11957,14 @@
       </c>
       <c r="N201" t="inlineStr">
         <is>
-          <t>First leg of the airport–downtown chain; transfer to Route 97 at UBCO Exchange.</t>
+          <t>No service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>local-bus:krt-97</t>
+          <t>local-bus:krt-23</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -11984,7 +11979,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>97 Okanagan</t>
+          <t>23 Lake Country</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -12023,14 +12018,14 @@
       </c>
       <c r="N202" t="inlineStr">
         <is>
-          <t>Second leg of the airport–downtown chain: UBCO Exchange to Queensway downtown.</t>
+          <t>First leg of the airport–downtown chain; transfer to Route 97 at UBCO Exchange.</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>local-bus:mtw-1</t>
+          <t>local-bus:krt-97</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12045,17 +12040,17 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>1/2 Port McNeill - Port Hardy</t>
+          <t>97 Okanagan</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Southern Interior</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -12063,12 +12058,12 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Port Hardy</t>
+          <t>Kelowna</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Port McNeill</t>
+          <t>Kelowna</t>
         </is>
       </c>
       <c r="J203" t="b">
@@ -12084,14 +12079,14 @@
       </c>
       <c r="N203" t="inlineStr">
         <is>
-          <t>Five trips a day on weekdays, two on Saturday, and no service on Sunday.</t>
+          <t>Second leg of the airport–downtown chain: UBCO Exchange to Queensway downtown.</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>local-bus:mtw-5</t>
+          <t>local-bus:mtw-1</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12106,7 +12101,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>5 Coal Harbour</t>
+          <t>1/2 Port McNeill - Port Hardy</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -12129,7 +12124,7 @@
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Coal Harbour</t>
+          <t>Port McNeill</t>
         </is>
       </c>
       <c r="J204" t="b">
@@ -12145,14 +12140,14 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>No service on Sunday.</t>
+          <t>Five trips a day on weekdays, two on Saturday, and no service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>local-bus:pg-161</t>
+          <t>local-bus:mtw-5</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12167,12 +12162,12 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>161 Prince George / Burns Lake</t>
+          <t>5 Coal Harbour</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Cariboo</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -12185,12 +12180,12 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Vanderhoof</t>
+          <t>Port Hardy</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>Prince George</t>
+          <t>Coal Harbour</t>
         </is>
       </c>
       <c r="J205" t="b">
@@ -12202,13 +12197,18 @@
       <c r="M205" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>No service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>local-bus:pg-162</t>
+          <t>local-bus:pg-161</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12223,12 +12223,12 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>162 Smithers / Burns Lake</t>
+          <t>161 Prince George / Burns Lake</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Northern BC</t>
+          <t>Cariboo</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -12241,12 +12241,12 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Smithers</t>
+          <t>Vanderhoof</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Burns Lake</t>
+          <t>Prince George</t>
         </is>
       </c>
       <c r="J206" t="b">
@@ -12258,18 +12258,13 @@
       <c r="M206" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>Runs Monday, Wednesday and Friday only.</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>local-bus:plr-12</t>
+          <t>local-bus:pg-162</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12284,12 +12279,12 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>12 Stillwater</t>
+          <t>162 Smithers / Burns Lake</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>qathet (Powell River) / Sunshine Coast</t>
+          <t>Northern BC</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -12302,12 +12297,12 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Stillwater</t>
+          <t>Smithers</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Powell River</t>
+          <t>Burns Lake</t>
         </is>
       </c>
       <c r="J207" t="b">
@@ -12319,13 +12314,18 @@
       <c r="M207" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Runs Monday, Wednesday and Friday only.</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>local-bus:plr-13</t>
+          <t>local-bus:plr-12</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12340,12 +12340,12 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>13 Texada Island</t>
+          <t>12 Stillwater</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Vancouver, Coast &amp; Mountains</t>
+          <t>qathet (Powell River) / Sunshine Coast</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Gillies Bay</t>
+          <t>Stillwater</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -12375,18 +12375,13 @@
       <c r="M208" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>Runs Tuesday and Thursday only.</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>local-bus:plr-14</t>
+          <t>local-bus:plr-13</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12401,12 +12396,12 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>14 Lund</t>
+          <t>13 Texada Island</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>qathet (Powell River) / Sunshine Coast</t>
+          <t>Vancouver, Coast &amp; Mountains</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -12419,14 +12414,14 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
+          <t>Gillies Bay</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
           <t>Powell River</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>Lund</t>
-        </is>
-      </c>
       <c r="J209" t="b">
         <v>1</v>
       </c>
@@ -12440,14 +12435,14 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>Runs Monday, Tuesday and Friday most of the year, six days a week from mid-May to Labour Day; some stretches are on-request. Front bike rack; e-bikes under 25 kg allowed.</t>
+          <t>Runs Tuesday and Thursday only.</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>local-bus:pmb-99</t>
+          <t>local-bus:plr-14</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12462,30 +12457,30 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>99 Pemberton Commuter</t>
+          <t>14 Lund</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Sea-to-Sky</t>
+          <t>qathet (Powell River) / Sunshine Coast</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G210" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Whistler</t>
+          <t>Powell River</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Pemberton</t>
+          <t>Lund</t>
         </is>
       </c>
       <c r="J210" t="b">
@@ -12497,13 +12492,18 @@
       <c r="M210" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>Runs Monday, Tuesday and Friday most of the year, six days a week from mid-May to Labour Day; some stretches are on-request. Front bike rack; e-bikes under 25 kg allowed.</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>local-bus:pr-55</t>
+          <t>local-bus:pmb-99</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12518,30 +12518,30 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>55 Fairview Bay</t>
+          <t>99 Pemberton Commuter</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>North</t>
+          <t>Sea-to-Sky</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G211" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Whistler</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Pemberton</t>
         </is>
       </c>
       <c r="J211" t="b">
@@ -12553,18 +12553,13 @@
       <c r="M211" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N211" t="inlineStr">
-        <is>
-          <t>Monday to Saturday only, about three trips a day; stops near the ferry terminal.</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>local-bus:qnl-30</t>
+          <t>local-bus:pr-55</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12579,12 +12574,12 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>30 Wells</t>
+          <t>55 Fairview Bay</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Cariboo</t>
+          <t>North</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -12597,12 +12592,12 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Quesnel</t>
+          <t>Prince Rupert</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Barkerville</t>
+          <t>Prince Rupert</t>
         </is>
       </c>
       <c r="J212" t="b">
@@ -12614,13 +12609,18 @@
       <c r="M212" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Monday to Saturday only, about three trips a day; stops near the ferry terminal.</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>local-bus:qnl-31</t>
+          <t>local-bus:qnl-30</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12635,12 +12635,12 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>31 Nazko</t>
+          <t>30 Wells</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Cariboo Chilcotin Coast</t>
+          <t>Cariboo</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -12658,7 +12658,7 @@
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Nazko</t>
+          <t>Barkerville</t>
         </is>
       </c>
       <c r="J213" t="b">
@@ -12670,18 +12670,13 @@
       <c r="M213" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>Wednesdays only.</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>local-bus:rdn-1</t>
+          <t>local-bus:qnl-31</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12696,17 +12691,17 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>1 Nanaimo Rapid Line</t>
+          <t>31 Nazko</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Cariboo Chilcotin Coast</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -12714,12 +12709,12 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Quesnel</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Nazko</t>
         </is>
       </c>
       <c r="J214" t="b">
@@ -12735,14 +12730,14 @@
       </c>
       <c r="N214" t="inlineStr">
         <is>
-          <t>Runs every 20 minutes or so, seven days a week.</t>
+          <t>Wednesdays only.</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>local-bus:rdn-20</t>
+          <t>local-bus:rdn-1</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12757,7 +12752,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>20/20A Hammond Bay / Dover</t>
+          <t>1 Nanaimo Rapid Line</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -12792,13 +12787,18 @@
       <c r="M215" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>Runs every 20 minutes or so, seven days a week.</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>local-bus:rdn-25</t>
+          <t>local-bus:rdn-20</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>25 Ferry Shuttle</t>
+          <t>20/20A Hammond Bay / Dover</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -12848,18 +12848,13 @@
       <c r="M216" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N216" t="inlineStr">
-        <is>
-          <t>Also serves the Hullo ferry and Helijet terminals at the Nanaimo Port Authority.</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>local-bus:rdn-70</t>
+          <t>local-bus:rdn-25</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12874,7 +12869,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>70 NCX Nanaimo - Cowichan Express</t>
+          <t>25 Ferry Shuttle</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -12888,7 +12883,7 @@
         </is>
       </c>
       <c r="G217" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H217" t="inlineStr">
         <is>
@@ -12897,7 +12892,7 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Duncan</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="J217" t="b">
@@ -12909,13 +12904,18 @@
       <c r="M217" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>Also serves the Hullo ferry and Helijet terminals at the Nanaimo Port Authority.</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>local-bus:rdn-9</t>
+          <t>local-bus:rdn-70</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12930,7 +12930,7 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>9 Intercity</t>
+          <t>70 NCX Nanaimo - Cowichan Express</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -12944,16 +12944,16 @@
         </is>
       </c>
       <c r="G218" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Qualicum Beach</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="J218" t="b">
@@ -12971,7 +12971,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>local-bus:rdn-99</t>
+          <t>local-bus:rdn-9</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>99 Deep Bay</t>
+          <t>9 Intercity</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -13000,7 +13000,7 @@
         </is>
       </c>
       <c r="G219" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H219" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Deep Bay</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="J219" t="b">
@@ -13027,7 +13027,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>local-bus:sc-1</t>
+          <t>local-bus:rdn-99</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13042,12 +13042,12 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>1 Sechelt-Gibsons/Langdale Ferry</t>
+          <t>99 Deep Bay</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Sunshine Coast</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -13060,12 +13060,12 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Gibsons</t>
+          <t>Qualicum Beach</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Sechelt</t>
+          <t>Deep Bay</t>
         </is>
       </c>
       <c r="J220" t="b">
@@ -13083,7 +13083,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>local-bus:sc-4</t>
+          <t>local-bus:sc-1</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13098,12 +13098,12 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>4 Halfmoon Bay</t>
+          <t>1 Sechelt-Gibsons/Langdale Ferry</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Vancouver, Coast &amp; Mountains</t>
+          <t>Sunshine Coast</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -13116,12 +13116,12 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
+          <t>Gibsons</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
           <t>Sechelt</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>Halfmoon Bay</t>
         </is>
       </c>
       <c r="J221" t="b">
@@ -13139,7 +13139,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>local-bus:sc-90</t>
+          <t>local-bus:sc-4</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>90 Sechelt-Gibsons/Langdale Ferry Express</t>
+          <t>4 Halfmoon Bay</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Sunshine Coast</t>
+          <t>Vancouver, Coast &amp; Mountains</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>Gibsons</t>
+          <t>Halfmoon Bay</t>
         </is>
       </c>
       <c r="J222" t="b">
@@ -13195,7 +13195,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>local-bus:skn-11</t>
+          <t>local-bus:sc-90</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -13210,17 +13210,17 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>11 Terrace-Kitimat Connector</t>
+          <t>90 Sechelt-Gibsons/Langdale Ferry Express</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>North Coast</t>
+          <t>Sunshine Coast</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -13228,12 +13228,12 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Terrace</t>
+          <t>Sechelt</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Kitimat</t>
+          <t>Gibsons</t>
         </is>
       </c>
       <c r="J223" t="b">
@@ -13251,7 +13251,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>local-bus:skn-14</t>
+          <t>local-bus:skn-11</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>14 Gitaus/Queensway</t>
+          <t>11 Terrace-Kitimat Connector</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Northern BC</t>
+          <t>North Coast</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -13289,7 +13289,7 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Usk</t>
+          <t>Kitimat</t>
         </is>
       </c>
       <c r="J224" t="b">
@@ -13301,18 +13301,13 @@
       <c r="M224" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>No service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>local-bus:skn-163</t>
+          <t>local-bus:skn-14</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -13327,7 +13322,7 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>163 Hazeltons/Smithers</t>
+          <t>14 Gitaus/Queensway</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -13345,12 +13340,12 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Smithers</t>
+          <t>Terrace</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Kispiox</t>
+          <t>Usk</t>
         </is>
       </c>
       <c r="J225" t="b">
@@ -13366,14 +13361,14 @@
       </c>
       <c r="N225" t="inlineStr">
         <is>
-          <t>Runs Monday, Wednesday and Friday only.</t>
+          <t>No service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>local-bus:skn-164</t>
+          <t>local-bus:skn-163</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -13388,7 +13383,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>164 Hazeltons/Terrace</t>
+          <t>163 Hazeltons/Smithers</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -13402,11 +13397,11 @@
         </is>
       </c>
       <c r="G226" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Terrace</t>
+          <t>Smithers</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -13427,14 +13422,14 @@
       </c>
       <c r="N226" t="inlineStr">
         <is>
-          <t>Runs Tuesday, Thursday and Saturday only.</t>
+          <t>Runs Monday, Wednesday and Friday only.</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>local-bus:skn-31</t>
+          <t>local-bus:skn-164</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -13449,7 +13444,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>31 Gitsegukla</t>
+          <t>164 Hazeltons/Terrace</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -13463,11 +13458,11 @@
         </is>
       </c>
       <c r="G227" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Kitseguecla</t>
+          <t>Terrace</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -13495,7 +13490,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>local-bus:skn-32</t>
+          <t>local-bus:skn-31</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -13510,7 +13505,7 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>32 West Connector</t>
+          <t>31 Gitsegukla</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -13528,12 +13523,12 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Hazelton</t>
+          <t>Kitseguecla</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Kitwanga</t>
+          <t>Kispiox</t>
         </is>
       </c>
       <c r="J228" t="b">
@@ -13549,14 +13544,14 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>Runs Monday, Wednesday and Friday only.</t>
+          <t>Runs Tuesday, Thursday and Saturday only.</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>local-bus:smi-23</t>
+          <t>local-bus:skn-32</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -13571,7 +13566,7 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>23 Smithers/Witset</t>
+          <t>32 West Connector</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -13589,12 +13584,12 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Moricetown</t>
+          <t>Hazelton</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Smithers</t>
+          <t>Kitwanga</t>
         </is>
       </c>
       <c r="J229" t="b">
@@ -13610,14 +13605,14 @@
       </c>
       <c r="N229" t="inlineStr">
         <is>
-          <t>No service on Sunday.</t>
+          <t>Runs Monday, Wednesday and Friday only.</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>local-bus:sok-30</t>
+          <t>local-bus:smi-23</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -13632,12 +13627,12 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>30 Penticton / Summerland</t>
+          <t>23 Smithers/Witset</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Southern Interior</t>
+          <t>Northern BC</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -13650,12 +13645,12 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Penticton</t>
+          <t>Moricetown</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>Summerland</t>
+          <t>Smithers</t>
         </is>
       </c>
       <c r="J230" t="b">
@@ -13667,13 +13662,18 @@
       <c r="M230" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>No service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>local-bus:sok-40</t>
+          <t>local-bus:sok-30</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -13688,7 +13688,7 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>40 Osoyoos / Penticton</t>
+          <t>30 Penticton / Summerland</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -13702,16 +13702,16 @@
         </is>
       </c>
       <c r="G231" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Osoyoos</t>
+          <t>Penticton</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>Penticton</t>
+          <t>Summerland</t>
         </is>
       </c>
       <c r="J231" t="b">
@@ -13729,7 +13729,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>local-bus:sok-50</t>
+          <t>local-bus:sok-40</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -13744,7 +13744,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>50 Penticton / Princeton</t>
+          <t>40 Osoyoos / Penticton</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -13762,7 +13762,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Princeton</t>
+          <t>Osoyoos</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -13785,7 +13785,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>local-bus:sok-70</t>
+          <t>local-bus:sok-50</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>70 Kelowna / Penticton</t>
+          <t>50 Penticton / Princeton</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -13814,16 +13814,16 @@
         </is>
       </c>
       <c r="G233" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H233" t="inlineStr">
         <is>
+          <t>Princeton</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
           <t>Penticton</t>
-        </is>
-      </c>
-      <c r="I233" t="inlineStr">
-        <is>
-          <t>Kelowna</t>
         </is>
       </c>
       <c r="J233" t="b">
@@ -13841,7 +13841,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>local-bus:tl-229</t>
+          <t>local-bus:sok-70</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -13851,35 +13851,35 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>TransLink</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>229 Lonsdale Quay / Lynn Valley</t>
+          <t>70 Kelowna / Penticton</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Metro Vancouver</t>
+          <t>Southern Interior</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G234" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>North Vancouver</t>
+          <t>Penticton</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>North Vancouver</t>
+          <t>Kelowna</t>
         </is>
       </c>
       <c r="J234" t="b">
@@ -13890,19 +13890,14 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
-        </is>
-      </c>
-      <c r="N234" t="inlineStr">
-        <is>
-          <t>Runs about every 30 minutes, seven days a week.</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>local-bus:tl-257</t>
+          <t>local-bus:tl-229</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -13917,7 +13912,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>257 Horseshoe Bay Express</t>
+          <t>229 Lonsdale Quay / Lynn Valley</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -13931,16 +13926,16 @@
         </is>
       </c>
       <c r="G235" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>West Vancouver</t>
+          <t>North Vancouver</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>North Vancouver</t>
         </is>
       </c>
       <c r="J235" t="b">
@@ -13952,13 +13947,18 @@
       <c r="M235" t="inlineStr">
         <is>
           <t>yes, with conditions</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>Runs about every 30 minutes, seven days a week.</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>local-bus:tl-262</t>
+          <t>local-bus:tl-257</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>262 Lions Bay-Brunswick (Community Shuttle)</t>
+          <t>257 Horseshoe Bay Express</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -13987,18 +13987,23 @@
         </is>
       </c>
       <c r="G236" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>West Vancouver</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Vancouver</t>
+        </is>
       </c>
       <c r="J236" t="b">
-        <v>0</v>
-      </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>reviewed and set aside</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L236" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M236" t="inlineStr">
         <is>
@@ -14009,7 +14014,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>local-bus:tl-620</t>
+          <t>local-bus:tl-262</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -14024,7 +14029,7 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>620 Bridgeport Station / Tsawwassen Ferry</t>
+          <t>262 Lions Bay-Brunswick (Community Shuttle)</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -14038,39 +14043,29 @@
         </is>
       </c>
       <c r="G237" t="n">
-        <v>3</v>
-      </c>
-      <c r="H237" t="inlineStr">
-        <is>
-          <t>Delta</t>
-        </is>
-      </c>
-      <c r="I237" t="inlineStr">
-        <is>
-          <t>Richmond</t>
-        </is>
+        <v>0</v>
       </c>
       <c r="J237" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>reviewed and set aside</t>
+        </is>
       </c>
       <c r="L237" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M237" t="inlineStr">
         <is>
           <t>yes, with conditions</t>
-        </is>
-      </c>
-      <c r="N237" t="inlineStr">
-        <is>
-          <t>The 620 is year-round, roughly hourly, timed to sailings, with two bike-rack spots. On busy summer ferry days the seasonal 900 Bike Bus can carry an extra 10 bikes.</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>local-bus:tl-701</t>
+          <t>local-bus:tl-620</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -14085,7 +14080,7 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>701 Coquitlam Central / Haney Place (daily core)</t>
+          <t>620 Bridgeport Station / Tsawwassen Ferry</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
@@ -14099,16 +14094,16 @@
         </is>
       </c>
       <c r="G238" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Coquitlam</t>
+          <t>Delta</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
         <is>
-          <t>Maple Ridge</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="J238" t="b">
@@ -14124,14 +14119,14 @@
       </c>
       <c r="N238" t="inlineStr">
         <is>
-          <t>Daily including weekends, about every 15–30 minutes.</t>
+          <t>The 620 is year-round, roughly hourly, timed to sailings, with two bike-rack spots. On busy summer ferry days the seasonal 900 Bike Bus can carry an extra 10 bikes.</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>local-bus:tl-701-mission</t>
+          <t>local-bus:tl-701</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -14146,7 +14141,7 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>701 Haney Place / Mission City (weekday-only extension)</t>
+          <t>701 Coquitlam Central / Haney Place (daily core)</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -14156,7 +14151,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -14164,14 +14159,14 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
+          <t>Coquitlam</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
           <t>Maple Ridge</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr">
-        <is>
-          <t>Mission</t>
-        </is>
-      </c>
       <c r="J239" t="b">
         <v>1</v>
       </c>
@@ -14185,14 +14180,14 @@
       </c>
       <c r="N239" t="inlineStr">
         <is>
-          <t>Weekday-only extension; it doesn't run on weekends, when the West Coast Express is also dark.</t>
+          <t>Daily including weekends, about every 15–30 minutes.</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>local-bus:tl-r2</t>
+          <t>local-bus:tl-701-mission</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -14207,7 +14202,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>R2 Marine Dr RapidBus</t>
+          <t>701 Haney Place / Mission City (weekday-only extension)</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -14217,7 +14212,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -14225,12 +14220,12 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>North Vancouver</t>
+          <t>Maple Ridge</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
         <is>
-          <t>West Vancouver</t>
+          <t>Mission</t>
         </is>
       </c>
       <c r="J240" t="b">
@@ -14246,14 +14241,14 @@
       </c>
       <c r="N240" t="inlineStr">
         <is>
-          <t>Frequent service, seven days a week.</t>
+          <t>Weekday-only extension; it doesn't run on weekends, when the West Coast Express is also dark.</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>local-bus:vrt-51x</t>
+          <t>local-bus:tl-r2</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -14263,35 +14258,35 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>BC Transit</t>
+          <t>TransLink</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>51X Westhills Exch / UVic Express</t>
+          <t>R2 Marine Dr RapidBus</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Metro Vancouver</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G241" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Langford</t>
+          <t>North Vancouver</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Saanich</t>
+          <t>West Vancouver</t>
         </is>
       </c>
       <c r="J241" t="b">
@@ -14302,19 +14297,19 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
         <is>
-          <t>Weekdays only.</t>
+          <t>Frequent service, seven days a week.</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>local-bus:vrt-61</t>
+          <t>local-bus:vrt-51x</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -14329,7 +14324,7 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>61 Sooke / Langford / Downtown</t>
+          <t>51X Westhills Exch / UVic Express</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -14339,20 +14334,20 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G242" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Langford</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Sooke</t>
+          <t>Saanich</t>
         </is>
       </c>
       <c r="J242" t="b">
@@ -14364,13 +14359,18 @@
       <c r="M242" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>Weekdays only.</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>local-bus:vrt-64</t>
+          <t>local-bus:vrt-61</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -14385,7 +14385,7 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>64 Langford Exch / Sooke via E Sooke and Beecher Bay</t>
+          <t>61 Sooke / Langford / Downtown</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
@@ -14395,20 +14395,20 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G243" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H243" t="inlineStr">
         <is>
+          <t>Victoria</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
           <t>Sooke</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>Colwood</t>
         </is>
       </c>
       <c r="J243" t="b">
@@ -14426,7 +14426,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>local-bus:vrt-65</t>
+          <t>local-bus:vrt-64</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -14441,7 +14441,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>65 Sooke / Downtown via Westhills</t>
+          <t>64 Langford Exch / Sooke via E Sooke and Beecher Bay</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
@@ -14455,16 +14455,16 @@
         </is>
       </c>
       <c r="G244" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Sooke</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Sooke</t>
+          <t>Colwood</t>
         </is>
       </c>
       <c r="J244" t="b">
@@ -14482,7 +14482,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>local-bus:vrt-70</t>
+          <t>local-bus:vrt-65</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -14497,7 +14497,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>70 Swartz Bay / Downtown</t>
+          <t>65 Sooke / Downtown via Westhills</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
@@ -14507,11 +14507,11 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G245" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H245" t="inlineStr">
         <is>
@@ -14520,7 +14520,7 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Sooke</t>
         </is>
       </c>
       <c r="J245" t="b">
@@ -14538,7 +14538,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>local-bus:vrt-71</t>
+          <t>local-bus:vrt-70</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -14553,7 +14553,7 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>71 Swartz Bay / Downtown</t>
+          <t>70 Swartz Bay / Downtown</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>Sidney</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="J246" t="b">
@@ -14588,18 +14588,13 @@
       <c r="M246" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N246" t="inlineStr">
-        <is>
-          <t>Weekdays only.</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>local-bus:vrt-72</t>
+          <t>local-bus:vrt-71</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -14614,7 +14609,7 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>72 Swartz Bay / Downtown (via Saanichton)</t>
+          <t>71 Swartz Bay / Downtown</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
@@ -14624,7 +14619,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -14637,7 +14632,7 @@
       </c>
       <c r="I247" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Sidney</t>
         </is>
       </c>
       <c r="J247" t="b">
@@ -14653,14 +14648,14 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>Via Saanichton; a parallel option to the 70.</t>
+          <t>Weekdays only.</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>local-bus:vrt-75</t>
+          <t>local-bus:vrt-72</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -14675,7 +14670,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>75 Saanichton / Royal Oak / Downtown</t>
+          <t>72 Swartz Bay / Downtown (via Saanichton)</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -14698,7 +14693,7 @@
       </c>
       <c r="I248" t="inlineStr">
         <is>
-          <t>Central Saanich</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="J248" t="b">
@@ -14710,13 +14705,18 @@
       <c r="M248" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>Via Saanichton; a parallel option to the 70.</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>local-bus:vrt-76</t>
+          <t>local-bus:vrt-75</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>76 Swartz Bay / UVic</t>
+          <t>75 Saanichton / Royal Oak / Downtown</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -14749,12 +14749,12 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>North Saanich</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Saanich</t>
+          <t>Central Saanich</t>
         </is>
       </c>
       <c r="J249" t="b">
@@ -14766,18 +14766,13 @@
       <c r="M249" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N249" t="inlineStr">
-        <is>
-          <t>Toward Swartz Bay it runs Friday only; toward UVic, Sunday and Monday only.</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>local-bus:vrt-83</t>
+          <t>local-bus:vrt-76</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -14792,7 +14787,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>83 Sidney / Brentwood / Royal Oak</t>
+          <t>76 Swartz Bay / UVic</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -14802,7 +14797,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -14810,7 +14805,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Sidney</t>
+          <t>North Saanich</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -14827,13 +14822,18 @@
       <c r="M250" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>Toward Swartz Bay it runs Friday only; toward UVic, Sunday and Monday only.</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>local-bus:vs-41</t>
+          <t>local-bus:vrt-83</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -14848,17 +14848,17 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>41 Salmon Arm-Enderby</t>
+          <t>83 Sidney / Brentwood / Royal Oak</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Thompson Okanagan</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -14866,12 +14866,12 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Enderby</t>
+          <t>Sidney</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
         <is>
-          <t>Salmon Arm</t>
+          <t>Saanich</t>
         </is>
       </c>
       <c r="J251" t="b">
@@ -14883,18 +14883,13 @@
       <c r="M251" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N251" t="inlineStr">
-        <is>
-          <t>Wednesdays only.</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>local-bus:vs-42</t>
+          <t>local-bus:vs-41</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -14909,7 +14904,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>42 Salmon Arm-Eagle Bay</t>
+          <t>41 Salmon Arm-Enderby</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -14927,14 +14922,14 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
+          <t>Enderby</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
           <t>Salmon Arm</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>Carlin</t>
-        </is>
-      </c>
       <c r="J252" t="b">
         <v>1</v>
       </c>
@@ -14948,14 +14943,14 @@
       </c>
       <c r="N252" t="inlineStr">
         <is>
-          <t>Thursdays only.</t>
+          <t>Wednesdays only.</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>local-bus:vs-43</t>
+          <t>local-bus:vs-42</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -14970,7 +14965,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>43 Salmon Arm-Sorrento</t>
+          <t>42 Salmon Arm-Eagle Bay</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -14993,7 +14988,7 @@
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>Sorrento</t>
+          <t>Carlin</t>
         </is>
       </c>
       <c r="J253" t="b">
@@ -15016,7 +15011,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>local-bus:vs-60</t>
+          <t>local-bus:vs-43</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -15031,7 +15026,7 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>60 Enderby/Vernon</t>
+          <t>43 Salmon Arm-Sorrento</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -15045,16 +15040,16 @@
         </is>
       </c>
       <c r="G254" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Enderby</t>
+          <t>Salmon Arm</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>Vernon</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="J254" t="b">
@@ -15070,14 +15065,14 @@
       </c>
       <c r="N254" t="inlineStr">
         <is>
-          <t>No service on Sunday.</t>
+          <t>Thursdays only.</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>local-bus:vs-61</t>
+          <t>local-bus:vs-60</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -15092,7 +15087,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>61 Lumby/Vernon</t>
+          <t>60 Enderby/Vernon</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -15106,11 +15101,11 @@
         </is>
       </c>
       <c r="G255" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Lumby</t>
+          <t>Enderby</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -15131,14 +15126,14 @@
       </c>
       <c r="N255" t="inlineStr">
         <is>
-          <t>Weekdays only.</t>
+          <t>No service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>local-bus:vs-90</t>
+          <t>local-bus:vs-61</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -15153,25 +15148,25 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>90 UBCO/Vernon</t>
+          <t>61 Lumby/Vernon</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Southern Interior</t>
+          <t>Thompson Okanagan</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G256" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Kelowna</t>
+          <t>Lumby</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -15188,13 +15183,18 @@
       <c r="M256" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>Weekdays only.</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>local-bus:wct-1</t>
+          <t>local-bus:vs-90</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -15204,17 +15204,17 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>West Coast Transit System (Tofino/Ucluelet)</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>1 Tofino / Ucluelet</t>
+          <t>90 UBCO/Vernon</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Southern Interior</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -15227,12 +15227,12 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Ucluelet</t>
+          <t>Kelowna</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Tofino</t>
+          <t>Vernon</t>
         </is>
       </c>
       <c r="J257" t="b">
@@ -15250,7 +15250,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>local-bus:wk-10</t>
+          <t>local-bus:wct-1</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -15260,22 +15260,22 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>BC Transit</t>
+          <t>West Coast Transit System (Tofino/Ucluelet)</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>10 North Shore</t>
+          <t>1 Tofino / Ucluelet</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Kootenay Rockies</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -15283,12 +15283,12 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Nelson</t>
+          <t>Ucluelet</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>Balfour</t>
+          <t>Tofino</t>
         </is>
       </c>
       <c r="J258" t="b">
@@ -15300,18 +15300,13 @@
       <c r="M258" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N258" t="inlineStr">
-        <is>
-          <t>No service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>local-bus:wk-10x</t>
+          <t>local-bus:wk-10</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -15326,7 +15321,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>10X North Shore Express</t>
+          <t>10 North Shore</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -15372,7 +15367,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>local-bus:wk-20</t>
+          <t>local-bus:wk-10x</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -15387,7 +15382,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>20 Slocan Valley</t>
+          <t>10X North Shore Express</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -15401,16 +15396,16 @@
         </is>
       </c>
       <c r="G260" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Slocan</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Nelson</t>
+          <t>Balfour</t>
         </is>
       </c>
       <c r="J260" t="b">
@@ -15433,7 +15428,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>local-bus:wk-38</t>
+          <t>local-bus:wk-20</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -15448,7 +15443,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>38 Playmor via Pass Creek</t>
+          <t>20 Slocan Valley</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
@@ -15462,16 +15457,16 @@
         </is>
       </c>
       <c r="G261" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Castlegar</t>
+          <t>Slocan</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Brilliant</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="J261" t="b">
@@ -15487,14 +15482,14 @@
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>Runs Tuesday and Friday only.</t>
+          <t>No service on Sunday.</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>local-bus:wk-45</t>
+          <t>local-bus:wk-38</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -15509,12 +15504,12 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>45 Teck</t>
+          <t>38 Playmor via Pass Creek</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>West Kootenay</t>
+          <t>Kootenay Rockies</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -15523,16 +15518,16 @@
         </is>
       </c>
       <c r="G262" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Rossland</t>
+          <t>Castlegar</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Trail</t>
+          <t>Brilliant</t>
         </is>
       </c>
       <c r="J262" t="b">
@@ -15544,13 +15539,18 @@
       <c r="M262" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>Runs Tuesday and Friday only.</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>local-bus:wk-46</t>
+          <t>local-bus:wk-45</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>46 Rossland</t>
+          <t>45 Teck</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -15583,12 +15583,12 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
+          <t>Rossland</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
           <t>Trail</t>
-        </is>
-      </c>
-      <c r="I263" t="inlineStr">
-        <is>
-          <t>Rossland</t>
         </is>
       </c>
       <c r="J263" t="b">
@@ -15606,7 +15606,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>local-bus:wk-52</t>
+          <t>local-bus:wk-46</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -15621,12 +15621,12 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>52 Nakusp-Playmor via Silverton</t>
+          <t>46 Rossland</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Kootenay Rockies</t>
+          <t>West Kootenay</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -15639,12 +15639,12 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Nakusp</t>
+          <t>Trail</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Slocan</t>
+          <t>Rossland</t>
         </is>
       </c>
       <c r="J264" t="b">
@@ -15656,18 +15656,13 @@
       <c r="M264" t="inlineStr">
         <is>
           <t>yes</t>
-        </is>
-      </c>
-      <c r="N264" t="inlineStr">
-        <is>
-          <t>Wednesdays only.</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>local-bus:wk-53</t>
+          <t>local-bus:wk-52</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -15682,7 +15677,7 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>53 Nakusp-Edgewood</t>
+          <t>52 Nakusp-Playmor via Silverton</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -15696,7 +15691,7 @@
         </is>
       </c>
       <c r="G265" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -15705,7 +15700,7 @@
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Edgewood</t>
+          <t>Slocan</t>
         </is>
       </c>
       <c r="J265" t="b">
@@ -15721,14 +15716,14 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>Fridays only.</t>
+          <t>Wednesdays only.</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>local-bus:wk-58</t>
+          <t>local-bus:wk-53</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -15743,7 +15738,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>58 Kaslo-Argenta</t>
+          <t>53 Nakusp-Edgewood</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -15757,16 +15752,16 @@
         </is>
       </c>
       <c r="G266" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Kaslo</t>
+          <t>Nakusp</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Argenta</t>
+          <t>Edgewood</t>
         </is>
       </c>
       <c r="J266" t="b">
@@ -15782,14 +15777,14 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>Thursdays only.</t>
+          <t>Fridays only.</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>local-bus:wk-72</t>
+          <t>local-bus:wk-58</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -15804,7 +15799,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>72 Salmo-Nelson via Ymir</t>
+          <t>58 Kaslo-Argenta</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
@@ -15822,12 +15817,12 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Nelson</t>
+          <t>Kaslo</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Salmo</t>
+          <t>Argenta</t>
         </is>
       </c>
       <c r="J267" t="b">
@@ -15843,14 +15838,14 @@
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>Runs Tuesday, Thursday and Friday only.</t>
+          <t>Thursdays only.</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>local-bus:wk-74</t>
+          <t>local-bus:wk-72</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -15865,7 +15860,7 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>74 Nakusp-Nelson</t>
+          <t>72 Salmo-Nelson via Ymir</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
@@ -15883,12 +15878,12 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Nakusp</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Nelson</t>
+          <t>Salmo</t>
         </is>
       </c>
       <c r="J268" t="b">
@@ -15904,14 +15899,14 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>Runs Tuesday and Thursday only.</t>
+          <t>Runs Tuesday, Thursday and Friday only.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>local-bus:wk-76</t>
+          <t>local-bus:wk-74</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -15926,7 +15921,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>76 Kaslo-Nelson</t>
+          <t>74 Nakusp-Nelson</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -15940,18 +15935,18 @@
         </is>
       </c>
       <c r="G269" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H269" t="inlineStr">
         <is>
+          <t>Nakusp</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
           <t>Nelson</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>Kaslo</t>
-        </is>
-      </c>
       <c r="J269" t="b">
         <v>1</v>
       </c>
@@ -15965,14 +15960,14 @@
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>Runs Tuesday, Wednesday and Thursday only.</t>
+          <t>Runs Tuesday and Thursday only.</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>local-bus:wk-98</t>
+          <t>local-bus:wk-76</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -15987,12 +15982,12 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>98 Columbia Connector</t>
+          <t>76 Kaslo-Nelson</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>West Kootenay</t>
+          <t>Kootenay Rockies</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -16001,16 +15996,16 @@
         </is>
       </c>
       <c r="G270" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Castlegar</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Trail</t>
+          <t>Kaslo</t>
         </is>
       </c>
       <c r="J270" t="b">
@@ -16022,13 +16017,18 @@
       <c r="M270" t="inlineStr">
         <is>
           <t>yes</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>Runs Tuesday, Wednesday and Thursday only.</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>local-bus:wk-99</t>
+          <t>local-bus:wk-98</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -16043,7 +16043,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>99 Kootenay Connector</t>
+          <t>98 Columbia Connector</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
@@ -16061,12 +16061,12 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Nelson</t>
+          <t>Castlegar</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Castlegar</t>
+          <t>Trail</t>
         </is>
       </c>
       <c r="J271" t="b">
@@ -16084,27 +16084,27 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>local-train:WCE</t>
+          <t>local-bus:wk-99</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>local-train</t>
+          <t>local-bus</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>TransLink (West Coast Express)</t>
+          <t>BC Transit</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>West Coast Express</t>
+          <t>99 Kootenay Connector</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Metro Vancouver / Fraser Valley</t>
+          <t>West Kootenay</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -16113,16 +16113,16 @@
         </is>
       </c>
       <c r="G272" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Nelson</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Mission</t>
+          <t>Castlegar</t>
         </is>
       </c>
       <c r="J272" t="b">
@@ -16133,70 +16133,75 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
-        </is>
-      </c>
-      <c r="N272" t="inlineStr">
-        <is>
-          <t>Weekdays only, peak direction only: five trains toward Vancouver in the morning, five back in the evening.</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>rental:bud-cr-nan</t>
+          <t>local-train:WCE</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>rental-car</t>
+          <t>local-train</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Budget</t>
+          <t>TransLink (West Coast Express)</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>One-way rental: Campbell River – Nanaimo</t>
+          <t>West Coast Express</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Vancouver Island</t>
+          <t>Metro Vancouver / Fraser Valley</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G273" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Campbell River</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Mission</t>
         </is>
       </c>
       <c r="J273" t="b">
         <v>1</v>
       </c>
       <c r="L273" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M273" t="inlineStr">
         <is>
           <t>yes, with conditions</t>
+        </is>
+      </c>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>Weekdays only, peak direction only: five trains toward Vancouver in the morning, five back in the evening.</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>rental:bud-nan-vic</t>
+          <t>rental:bud-cr-nan</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -16211,7 +16216,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>One-way rental: Nanaimo – Victoria</t>
+          <t>One-way rental: Campbell River – Nanaimo</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -16224,12 +16229,12 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
+          <t>Campbell River</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
           <t>Nanaimo</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>Victoria</t>
         </is>
       </c>
       <c r="J274" t="b">
@@ -16247,7 +16252,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>rental:bud-pa-nan</t>
+          <t>rental:bud-nan-vic</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -16262,7 +16267,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>One-way rental: Port Alberni – Nanaimo</t>
+          <t>One-way rental: Nanaimo – Victoria</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
@@ -16275,12 +16280,12 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Port Alberni</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="J275" t="b">
@@ -16298,7 +16303,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>rental:bud-ph-nan</t>
+          <t>rental:bud-pa-nan</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -16313,7 +16318,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>One-way rental: Port Hardy – Nanaimo</t>
+          <t>One-way rental: Port Alberni – Nanaimo</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -16326,7 +16331,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Port Hardy</t>
+          <t>Port Alberni</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -16349,7 +16354,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>rental:nat-cr-cx</t>
+          <t>rental:bud-ph-nan</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -16359,12 +16364,12 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>National Car &amp; Truck Rental (Vancouver Island)</t>
+          <t>Budget</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>One-way rental: Campbell River – Comox</t>
+          <t>One-way rental: Port Hardy – Nanaimo</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -16377,12 +16382,12 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Campbell River</t>
+          <t>Port Hardy</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Comox</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="J277" t="b">
@@ -16400,7 +16405,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>rental:nat-cr-nan</t>
+          <t>rental:nat-cr-cx</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -16415,7 +16420,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>One-way rental: Campbell River – Nanaimo</t>
+          <t>One-way rental: Campbell River – Comox</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -16433,7 +16438,7 @@
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Comox</t>
         </is>
       </c>
       <c r="J278" t="b">
@@ -16451,7 +16456,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>rental:nat-cr-ph</t>
+          <t>rental:nat-cr-nan</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -16466,7 +16471,7 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>One-way rental: Campbell River – Port Hardy</t>
+          <t>One-way rental: Campbell River – Nanaimo</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
@@ -16484,7 +16489,7 @@
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>Port Hardy</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="J279" t="b">
@@ -16502,7 +16507,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>rental:nat-cx-nan</t>
+          <t>rental:nat-cr-ph</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -16517,7 +16522,7 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>One-way rental: Comox – Nanaimo</t>
+          <t>One-way rental: Campbell River – Port Hardy</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
@@ -16530,12 +16535,12 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Comox</t>
+          <t>Campbell River</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Port Hardy</t>
         </is>
       </c>
       <c r="J280" t="b">
@@ -16553,7 +16558,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>rental:nat-cx-ph</t>
+          <t>rental:nat-cx-nan</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -16568,7 +16573,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>One-way rental: Comox – Port Hardy</t>
+          <t>One-way rental: Comox – Nanaimo</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -16586,7 +16591,7 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>Port Hardy</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="J281" t="b">
@@ -16604,7 +16609,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>rental:nat-nan-vic</t>
+          <t>rental:nat-cx-ph</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -16619,7 +16624,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>One-way rental: Nanaimo – Victoria</t>
+          <t>One-way rental: Comox – Port Hardy</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -16632,12 +16637,12 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Comox</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Port Hardy</t>
         </is>
       </c>
       <c r="J282" t="b">
@@ -16655,7 +16660,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>rental:nat-ph-nan</t>
+          <t>rental:nat-nan-vic</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -16670,7 +16675,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>One-way rental: Port Hardy – Nanaimo</t>
+          <t>One-way rental: Nanaimo – Victoria</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -16683,12 +16688,12 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Port Hardy</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Nanaimo</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="J283" t="b">
@@ -16706,52 +16711,47 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>skytrain:1</t>
+          <t>rental:nat-ph-nan</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>skytrain</t>
+          <t>rental-car</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>TransLink</t>
+          <t>National Car &amp; Truck Rental (Vancouver Island)</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>SkyTrain (all lines)</t>
+          <t>One-way rental: Port Hardy – Nanaimo</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Metro Vancouver</t>
-        </is>
-      </c>
-      <c r="F284" t="inlineStr">
-        <is>
-          <t>daily</t>
+          <t>Vancouver Island</t>
         </is>
       </c>
       <c r="G284" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Port Hardy</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Nanaimo</t>
         </is>
       </c>
       <c r="J284" t="b">
         <v>1</v>
       </c>
       <c r="L284" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M284" t="inlineStr">
         <is>
@@ -16762,27 +16762,27 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>train:amtrak-cascades</t>
+          <t>skytrain:1</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>intercity-train</t>
+          <t>skytrain</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Amtrak Cascades</t>
+          <t>TransLink</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>Vancouver – Seattle (Cascades)</t>
+          <t>SkyTrain (all lines)</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>cross-border</t>
+          <t>Metro Vancouver</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -16791,16 +16791,16 @@
         </is>
       </c>
       <c r="G285" t="n">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Vancouver Pacific Central</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>Seattle Downtown WA</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="J285" t="b">
@@ -16812,18 +16812,13 @@
       <c r="M285" t="inlineStr">
         <is>
           <t>yes, with conditions</t>
-        </is>
-      </c>
-      <c r="N285" t="inlineStr">
-        <is>
-          <t>Two daily round trips from Pacific Central; reserve bike space when you book. Passport required.</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>train:via-canadian</t>
+          <t>train:amtrak-cascades</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -16833,26 +16828,26 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>VIA Rail</t>
+          <t>Amtrak Cascades</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>The Canadian (Vancouver – Kamloops North – Jasper)</t>
+          <t>Vancouver – Seattle (Cascades)</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>southwest</t>
+          <t>cross-border</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G286" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H286" t="inlineStr">
         <is>
@@ -16861,7 +16856,7 @@
       </c>
       <c r="I286" t="inlineStr">
         <is>
-          <t>Jasper AB</t>
+          <t>Seattle Downtown WA</t>
         </is>
       </c>
       <c r="J286" t="b">
@@ -16877,14 +16872,14 @@
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>Two departures a week in season; bikes can be checked on and off at Vancouver and Jasper only.</t>
+          <t>Two daily round trips from Pacific Central; reserve bike space when you book. Passport required.</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>train:via-skeena</t>
+          <t>train:via-canadian</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -16899,12 +16894,12 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>Skeena (Prince Rupert – Prince George – Jasper)</t>
+          <t>The Canadian (Vancouver – Kamloops North – Jasper)</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>north</t>
+          <t>southwest</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -16913,11 +16908,11 @@
         </is>
       </c>
       <c r="G287" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Vancouver Pacific Central</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -16938,70 +16933,75 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>Three departures a week; the trip includes an overnight stop in Prince George (book your own hotel).</t>
+          <t>Two departures a week in season; bikes can be checked on and off at Vancouver and Jasper only.</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>water-taxi:wt001</t>
+          <t>train:via-skeena</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>water-taxi</t>
+          <t>intercity-train</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Victoria Harbour Ferry</t>
+          <t>VIA Rail</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Empress Dock – Fisherman's Wharf</t>
+          <t>Skeena (Prince Rupert – Prince George – Jasper)</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Capital (Greater Victoria)</t>
+          <t>north</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G288" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Victoria</t>
+          <t>Prince Rupert</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Esquimalt</t>
+          <t>Jasper AB</t>
         </is>
       </c>
       <c r="J288" t="b">
-        <v>0</v>
-      </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L288" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes, with conditions</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>Three departures a week; the trip includes an overnight stop in Prince George (book your own hotel).</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>water-taxi:wt002</t>
+          <t>water-taxi:wt001</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>Empress Dock – Selkirk Landing (Gorge)</t>
+          <t>Empress Dock – Fisherman's Wharf</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -17025,7 +17025,7 @@
         </is>
       </c>
       <c r="G289" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H289" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Victoria (Victoria West)</t>
+          <t>Esquimalt</t>
         </is>
       </c>
       <c r="J289" t="b">
@@ -17057,7 +17057,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>water-taxi:wt003</t>
+          <t>water-taxi:wt002</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -17067,30 +17067,30 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>BLAST (English Bay Launch)</t>
+          <t>Victoria Harbour Ferry</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>Snug Cove – Coal Harbour</t>
+          <t>Empress Dock – Selkirk Landing (Gorge)</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Metro Vancouver / Howe Sound</t>
+          <t>Capital (Greater Victoria)</t>
         </is>
       </c>
       <c r="G290" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Bowen Island</t>
+          <t>Victoria</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>Vancouver</t>
+          <t>Victoria (Victoria West)</t>
         </is>
       </c>
       <c r="J290" t="b">
@@ -17098,7 +17098,7 @@
       </c>
       <c r="K290" t="inlineStr">
         <is>
-          <t>no longer operating</t>
+          <t>charter only, not a scheduled service</t>
         </is>
       </c>
       <c r="L290" t="b">
@@ -17109,16 +17109,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="N290" t="inlineStr">
-        <is>
-          <t>Weekday commuter water taxi, by reservation.</t>
-        </is>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>water-taxi:wt004</t>
+          <t>water-taxi:wt003</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -17133,7 +17128,7 @@
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Snug Cove – Granville Island</t>
+          <t>Snug Cove – Coal Harbour</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
@@ -17172,14 +17167,14 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>Summer-weekend service to Granville Island.</t>
+          <t>Weekday commuter water taxi, by reservation.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>water-taxi:wt005</t>
+          <t>water-taxi:wt004</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -17189,12 +17184,12 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Cormorant Marine Water Taxi</t>
+          <t>BLAST (English Bay Launch)</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Horseshoe Bay – Snug Cove</t>
+          <t>Snug Cove – Granville Island</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
@@ -17202,22 +17197,17 @@
           <t>Metro Vancouver / Howe Sound</t>
         </is>
       </c>
-      <c r="F292" t="inlineStr">
-        <is>
-          <t>on-demand</t>
-        </is>
-      </c>
       <c r="G292" t="n">
         <v>2</v>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>West Vancouver</t>
+          <t>Bowen Island</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>Bowen Island</t>
+          <t>Vancouver</t>
         </is>
       </c>
       <c r="J292" t="b">
@@ -17225,7 +17215,7 @@
       </c>
       <c r="K292" t="inlineStr">
         <is>
-          <t>charter only, not a scheduled service</t>
+          <t>no longer operating</t>
         </is>
       </c>
       <c r="L292" t="b">
@@ -17236,11 +17226,16 @@
           <t>unknown</t>
         </is>
       </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>Summer-weekend service to Granville Island.</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>water-taxi:wt006</t>
+          <t>water-taxi:wt005</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -17255,7 +17250,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>Horseshoe Bay – Gambier Harbour</t>
+          <t>Horseshoe Bay – Snug Cove</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -17263,6 +17258,11 @@
           <t>Metro Vancouver / Howe Sound</t>
         </is>
       </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>on-demand</t>
+        </is>
+      </c>
       <c r="G293" t="n">
         <v>2</v>
       </c>
@@ -17273,7 +17273,7 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Gambier Island</t>
+          <t>Bowen Island</t>
         </is>
       </c>
       <c r="J293" t="b">
@@ -17296,7 +17296,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>water-taxi:wt007</t>
+          <t>water-taxi:wt006</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -17306,22 +17306,17 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Lund Water Taxi</t>
+          <t>Cormorant Marine Water Taxi</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Lund – Savary Island</t>
+          <t>Horseshoe Bay – Gambier Harbour</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>qathet (Powell River) / Sunshine Coast</t>
-        </is>
-      </c>
-      <c r="F294" t="inlineStr">
-        <is>
-          <t>daily</t>
+          <t>Metro Vancouver / Howe Sound</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -17329,35 +17324,35 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Lund</t>
+          <t>West Vancouver</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
         <is>
-          <t>Savary Island</t>
+          <t>Gambier Island</t>
         </is>
       </c>
       <c r="J294" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
       </c>
       <c r="L294" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M294" t="inlineStr">
         <is>
           <t>unknown</t>
-        </is>
-      </c>
-      <c r="N294" t="inlineStr">
-        <is>
-          <t>Year-round walk-on service, near-hourly in July and August; reservations required. E-bikes not carried (barge by arrangement).</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>water-taxi:wt008</t>
+          <t>water-taxi:wt007</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -17367,7 +17362,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Savary Island Ferry (Finn Bay Marine / Access Point Marine)</t>
+          <t>Lund Water Taxi</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -17380,6 +17375,11 @@
           <t>qathet (Powell River) / Sunshine Coast</t>
         </is>
       </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
       <c r="G295" t="n">
         <v>2</v>
       </c>
@@ -17394,15 +17394,10 @@
         </is>
       </c>
       <c r="J295" t="b">
-        <v>0</v>
-      </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t>no longer operating</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L295" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M295" t="inlineStr">
         <is>
@@ -17411,14 +17406,14 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>Departures about every 30 minutes, June to September, from behind the Lund Hotel; reservations required.</t>
+          <t>Year-round walk-on service, near-hourly in July and August; reservations required. E-bikes not carried (barge by arrangement).</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>water-taxi:wt009</t>
+          <t>water-taxi:wt008</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -17428,22 +17423,17 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Discovery Launch Water Taxi</t>
+          <t>Savary Island Ferry (Finn Bay Marine / Access Point Marine)</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>Campbell River – Cortes Island</t>
+          <t>Lund – Savary Island</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Strathcona / Discovery Islands</t>
-        </is>
-      </c>
-      <c r="F296" t="inlineStr">
-        <is>
-          <t>limited</t>
+          <t>qathet (Powell River) / Sunshine Coast</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -17451,19 +17441,24 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Campbell River</t>
+          <t>Lund</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>Cortes Island</t>
+          <t>Savary Island</t>
         </is>
       </c>
       <c r="J296" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>no longer operating</t>
+        </is>
       </c>
       <c r="L296" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M296" t="inlineStr">
         <is>
@@ -17472,14 +17467,14 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>Scheduled Fridays and Sundays in summer (also calls at Savary, Hernando and Lund); otherwise by charter.</t>
+          <t>Departures about every 30 minutes, June to September, from behind the Lund Hotel; reservations required.</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>water-taxi:wt010</t>
+          <t>water-taxi:wt009</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -17489,12 +17484,12 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Qaya Way West Transportation</t>
+          <t>Discovery Launch Water Taxi</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Campbell River – Savary Island</t>
+          <t>Campbell River – Cortes Island</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -17504,11 +17499,11 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>seasonal-varies</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G297" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H297" t="inlineStr">
         <is>
@@ -17517,7 +17512,7 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>Savary Island</t>
+          <t>Cortes Island</t>
         </is>
       </c>
       <c r="J297" t="b">
@@ -17533,14 +17528,14 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>Southern run daily June 26 to September 7, calling at Manson's Landing and Hernando; reservations required.</t>
+          <t>Scheduled Fridays and Sundays in summer (also calls at Savary, Hernando and Lund); otherwise by charter.</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>water-taxi:wt011</t>
+          <t>water-taxi:wt010</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -17550,35 +17545,35 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Ahous Hakuum (MHSS)</t>
+          <t>Qaya Way West Transportation</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>Tofino – Maaqutusiis (Ahousaht)</t>
+          <t>Campbell River – Savary Island</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Alberni-Clayoquot (West Coast Vancouver Island)</t>
+          <t>Strathcona / Discovery Islands</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>seasonal-varies</t>
         </is>
       </c>
       <c r="G298" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>Tofino</t>
+          <t>Campbell River</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>Ahousaht (Flores Island)</t>
+          <t>Savary Island</t>
         </is>
       </c>
       <c r="J298" t="b">
@@ -17594,14 +17589,14 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>Runs Monday to Friday year-round, plus Sundays in spring and summer, from Tofino's 1st Street Dock.</t>
+          <t>Southern run daily June 26 to September 7, calling at Manson's Landing and Hernando; reservations required.</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>water-taxi:wt012</t>
+          <t>water-taxi:wt011</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -17611,12 +17606,12 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Tofino Water Taxi</t>
+          <t>Ahous Hakuum (MHSS)</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>Tofino – Ahousaht (Flores Island)</t>
+          <t>Tofino – Maaqutusiis (Ahousaht)</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -17624,6 +17619,11 @@
           <t>Alberni-Clayoquot (West Coast Vancouver Island)</t>
         </is>
       </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
       <c r="G299" t="n">
         <v>2</v>
       </c>
@@ -17638,15 +17638,10 @@
         </is>
       </c>
       <c r="J299" t="b">
-        <v>0</v>
-      </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L299" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M299" t="inlineStr">
         <is>
@@ -17655,14 +17650,14 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>Electric zero-emission vessel; year-round; an Ahousaht access fee applies.</t>
+          <t>Runs Monday to Friday year-round, plus Sundays in spring and summer, from Tofino's 1st Street Dock.</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>water-taxi:wt013</t>
+          <t>water-taxi:wt012</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -17672,22 +17667,17 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Lasqueti Island Ferry (Western Pacific Marine)</t>
+          <t>Tofino Water Taxi</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>French Creek – False Bay</t>
+          <t>Tofino – Ahousaht (Flores Island)</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>qathet / Northern Gulf Islands</t>
-        </is>
-      </c>
-      <c r="F300" t="inlineStr">
-        <is>
-          <t>daily</t>
+          <t>Alberni-Clayoquot (West Coast Vancouver Island)</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -17695,35 +17685,40 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>French Creek (Qualicum Beach)</t>
+          <t>Tofino</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Lasqueti Island</t>
+          <t>Ahousaht (Flores Island)</t>
         </is>
       </c>
       <c r="J300" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
       </c>
       <c r="L300" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>yes, with conditions</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>Foot passengers and freight only, no cars; about an hour across, with no Tuesday sailings. Tickets sold on board.</t>
+          <t>Electric zero-emission vessel; year-round; an Ahousaht access fee applies.</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>water-taxi:wt014</t>
+          <t>water-taxi:wt013</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -17733,22 +17728,22 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>West Coast Launch</t>
+          <t>Lasqueti Island Ferry (Western Pacific Marine)</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Cow Bay (Prince Rupert) – Dodge Cove</t>
+          <t>French Creek – False Bay</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>North Coast</t>
+          <t>qathet / Northern Gulf Islands</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -17756,12 +17751,12 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>French Creek (Qualicum Beach)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
         <is>
-          <t>Dodge Cove (Digby Island)</t>
+          <t>Lasqueti Island</t>
         </is>
       </c>
       <c r="J301" t="b">
@@ -17772,19 +17767,19 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>Ferry-style service several days a week; the schedule varies by season.</t>
+          <t>Foot passengers and freight only, no cars; about an hour across, with no Tuesday sailings. Tickets sold on board.</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>water-taxi:wt015</t>
+          <t>water-taxi:wt014</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -17799,7 +17794,7 @@
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>Cow Bay (Prince Rupert) – Digby Island Airport</t>
+          <t>Cow Bay (Prince Rupert) – Dodge Cove</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -17822,7 +17817,7 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>Digby Island</t>
+          <t>Dodge Cove (Digby Island)</t>
         </is>
       </c>
       <c r="J302" t="b">
@@ -17838,14 +17833,14 @@
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>About ten minutes across, timed with the airport shuttle; give advance notice.</t>
+          <t>Ferry-style service several days a week; the schedule varies by season.</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>water-taxi:wt016</t>
+          <t>water-taxi:wt015</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -17860,7 +17855,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>Cow Bay (Prince Rupert) – Metlakatla</t>
+          <t>Cow Bay (Prince Rupert) – Digby Island Airport</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -17883,7 +17878,7 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>Metlakatla</t>
+          <t>Digby Island</t>
         </is>
       </c>
       <c r="J303" t="b">
@@ -17899,14 +17894,14 @@
       </c>
       <c r="N303" t="inlineStr">
         <is>
-          <t>About 30 minutes across; scheduled and charter service.</t>
+          <t>About ten minutes across, timed with the airport shuttle; give advance notice.</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>water-taxi:wt017</t>
+          <t>water-taxi:wt016</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -17921,7 +17916,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>Cow Bay (Prince Rupert) – Oona River</t>
+          <t>Cow Bay (Prince Rupert) – Metlakatla</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
@@ -17929,6 +17924,11 @@
           <t>North Coast</t>
         </is>
       </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
       <c r="G304" t="n">
         <v>2</v>
       </c>
@@ -17939,19 +17939,14 @@
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>Oona River (Porcher Island)</t>
+          <t>Metlakatla</t>
         </is>
       </c>
       <c r="J304" t="b">
-        <v>0</v>
-      </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L304" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M304" t="inlineStr">
         <is>
@@ -17960,14 +17955,14 @@
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>About an hour and a quarter to Porcher Island; call to arrange.</t>
+          <t>About 30 minutes across; scheduled and charter service.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>water-taxi:wt018</t>
+          <t>water-taxi:wt017</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -17977,12 +17972,12 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Metlakatla Ferry Service</t>
+          <t>West Coast Launch</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Prince Rupert (Cow Bay) – Metlakatla</t>
+          <t>Cow Bay (Prince Rupert) – Oona River</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
@@ -17990,13 +17985,8 @@
           <t>North Coast</t>
         </is>
       </c>
-      <c r="F305" t="inlineStr">
-        <is>
-          <t>limited</t>
-        </is>
-      </c>
       <c r="G305" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H305" t="inlineStr">
         <is>
@@ -18005,14 +17995,19 @@
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Oona River (Porcher Island)</t>
         </is>
       </c>
       <c r="J305" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
       </c>
       <c r="L305" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M305" t="inlineStr">
         <is>
@@ -18021,14 +18016,14 @@
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>Community ferry from Cow Bay, about 15 minutes across, with several departures Monday to Friday.</t>
+          <t>About an hour and a quarter to Porcher Island; call to arrange.</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>water-taxi:wt019</t>
+          <t>water-taxi:wt018</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -18038,30 +18033,35 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>SeaCoastal Water Taxi (Kitasoo Xai'xais)</t>
+          <t>Metlakatla Ferry Service</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>Bella Bella – Klemtu</t>
+          <t>Prince Rupert (Cow Bay) – Metlakatla</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Central Coast (Great Bear Rainforest)</t>
+          <t>North Coast</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>limited</t>
         </is>
       </c>
       <c r="G306" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Bella Bella</t>
+          <t>Prince Rupert</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>Klemtu</t>
+          <t>Prince Rupert</t>
         </is>
       </c>
       <c r="J306" t="b">
@@ -18077,14 +18077,14 @@
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>Scheduled run between Bella Bella and Klemtu; up to 12 passengers plus freight.</t>
+          <t>Community ferry from Cow Bay, about 15 minutes across, with several departures Monday to Friday.</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>water-taxi:wt020</t>
+          <t>water-taxi:wt019</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -18094,17 +18094,17 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Lund Water Taxi</t>
+          <t>SeaCoastal Water Taxi (Kitasoo Xai'xais)</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Lund – Sarah Point (Sunshine Coast Trail)</t>
+          <t>Bella Bella – Klemtu</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>qathet (Powell River) / Sunshine Coast</t>
+          <t>Central Coast (Great Bear Rainforest)</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -18112,24 +18112,19 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Lund</t>
+          <t>Bella Bella</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>Sarah Point (Malaspina Peninsula)</t>
+          <t>Klemtu</t>
         </is>
       </c>
       <c r="J307" t="b">
-        <v>0</v>
-      </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L307" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M307" t="inlineStr">
         <is>
@@ -18138,14 +18133,14 @@
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>By reservation; trailhead drop-off for the Sunshine Coast Trail (also Desolation Sound and Cortes).</t>
+          <t>Scheduled run between Bella Bella and Klemtu; up to 12 passengers plus freight.</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>water-taxi:wt021</t>
+          <t>water-taxi:wt020</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -18155,17 +18150,17 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Cape Scott Water Taxi (North Coast Trail Shuttle)</t>
+          <t>Lund Water Taxi</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>Port Hardy – Shushartie Bay</t>
+          <t>Lund – Sarah Point (Sunshine Coast Trail)</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Mount Waddington (North Vancouver Island)</t>
+          <t>qathet (Powell River) / Sunshine Coast</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -18173,12 +18168,12 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Port Hardy</t>
+          <t>Lund</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>Shushartie Bay (Cape Scott Park)</t>
+          <t>Sarah Point (Malaspina Peninsula)</t>
         </is>
       </c>
       <c r="J308" t="b">
@@ -18199,14 +18194,14 @@
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>Pre-booked North Coast Trail drop-off, about an hour; 7am departures when booked; beach landings depend on the tide.</t>
+          <t>By reservation; trailhead drop-off for the Sunshine Coast Trail (also Desolation Sound and Cortes).</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>water-taxi:wt022</t>
+          <t>water-taxi:wt021</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -18221,7 +18216,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>Port Hardy – Cape Sutil / Fisherman Bay</t>
+          <t>Port Hardy – Shushartie Bay</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -18230,7 +18225,7 @@
         </is>
       </c>
       <c r="G309" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H309" t="inlineStr">
         <is>
@@ -18239,7 +18234,7 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>Fisherman Bay (Cape Scott Park)</t>
+          <t>Shushartie Bay (Cape Scott Park)</t>
         </is>
       </c>
       <c r="J309" t="b">
@@ -18260,14 +18255,14 @@
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>Pre-booked alternate North Coast Trail access; high-tide-only landings, 6-person minimum to Fisherman Bay.</t>
+          <t>Pre-booked North Coast Trail drop-off, about an hour; 7am departures when booked; beach landings depend on the tide.</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>water-taxi:wt023</t>
+          <t>water-taxi:wt022</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -18282,21 +18277,16 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Port Hardy – Mid-Coast inlets</t>
+          <t>Port Hardy – Cape Sutil / Fisherman Bay</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Mount Waddington / Central Coast</t>
-        </is>
-      </c>
-      <c r="F310" t="inlineStr">
-        <is>
-          <t>on-demand</t>
+          <t>Mount Waddington (North Vancouver Island)</t>
         </is>
       </c>
       <c r="G310" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H310" t="inlineStr">
         <is>
@@ -18305,7 +18295,7 @@
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t>Calvert Island</t>
+          <t>Fisherman Bay (Cape Scott Park)</t>
         </is>
       </c>
       <c r="J310" t="b">
@@ -18313,7 +18303,7 @@
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t>on demand only, not a scheduled service</t>
+          <t>charter only, not a scheduled service</t>
         </is>
       </c>
       <c r="L310" t="b">
@@ -18324,11 +18314,16 @@
           <t>unknown</t>
         </is>
       </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>Pre-booked alternate North Coast Trail access; high-tide-only landings, 6-person minimum to Fisherman Bay.</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>water-taxi:wt024</t>
+          <t>water-taxi:wt023</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -18338,58 +18333,58 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Qaya Way West Transportation</t>
+          <t>Cape Scott Water Taxi (North Coast Trail Shuttle)</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Campbell River – Discovery Islands (Northern run)</t>
+          <t>Port Hardy – Mid-Coast inlets</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Strathcona / Discovery Islands</t>
+          <t>Mount Waddington / Central Coast</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>on-demand</t>
         </is>
       </c>
       <c r="G311" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Campbell River</t>
+          <t>Port Hardy</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>Hemming Bay</t>
+          <t>Calvert Island</t>
         </is>
       </c>
       <c r="J311" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>on demand only, not a scheduled service</t>
+        </is>
       </c>
       <c r="L311" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M311" t="inlineStr">
         <is>
           <t>unknown</t>
-        </is>
-      </c>
-      <c r="N311" t="inlineStr">
-        <is>
-          <t>Northern run Mondays and Fridays year-round, plus a seasonal Wednesday sailing; reservations required.</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>water-taxi:wt025</t>
+          <t>water-taxi:wt024</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -18399,12 +18394,12 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Discovery Launch Water Taxi</t>
+          <t>Qaya Way West Transportation</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Campbell River – Discovery Islands &amp; Mainland Inlets</t>
+          <t>Campbell River – Discovery Islands (Northern run)</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
@@ -18412,8 +18407,13 @@
           <t>Strathcona / Discovery Islands</t>
         </is>
       </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
       <c r="G312" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
@@ -18422,30 +18422,30 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>Bute Inlet (mainland)</t>
+          <t>Hemming Bay</t>
         </is>
       </c>
       <c r="J312" t="b">
-        <v>0</v>
-      </c>
-      <c r="K312" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L312" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M312" t="inlineStr">
         <is>
           <t>unknown</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>Northern run Mondays and Fridays year-round, plus a seasonal Wednesday sailing; reservations required.</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>water-taxi:wt026</t>
+          <t>water-taxi:wt025</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -18455,12 +18455,12 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Blind Channel Water Taxi</t>
+          <t>Discovery Launch Water Taxi</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>Blind Channel (West Thurlow) – Outer Discovery Islands</t>
+          <t>Campbell River – Discovery Islands &amp; Mainland Inlets</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -18469,16 +18469,16 @@
         </is>
       </c>
       <c r="G313" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Blind Channel (West Thurlow Island)</t>
+          <t>Campbell River</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>Quadra Island</t>
+          <t>Bute Inlet (mainland)</t>
         </is>
       </c>
       <c r="J313" t="b">
@@ -18501,7 +18501,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>water-taxi:wt027</t>
+          <t>water-taxi:wt026</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -18511,12 +18511,12 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Discovery West Adventures</t>
+          <t>Blind Channel Water Taxi</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Campbell River – Outer Discovery Islands</t>
+          <t>Blind Channel (West Thurlow) – Outer Discovery Islands</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
@@ -18525,16 +18525,16 @@
         </is>
       </c>
       <c r="G314" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Campbell River</t>
+          <t>Blind Channel (West Thurlow Island)</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t>Frederick Arm (mainland)</t>
+          <t>Quadra Island</t>
         </is>
       </c>
       <c r="J314" t="b">
@@ -18557,7 +18557,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>water-taxi:wt028</t>
+          <t>water-taxi:wt027</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -18567,12 +18567,12 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Sutil Charters</t>
+          <t>Discovery West Adventures</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>Quadra Island – Cortes Island</t>
+          <t>Campbell River – Outer Discovery Islands</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -18581,16 +18581,16 @@
         </is>
       </c>
       <c r="G315" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Quadra Island</t>
+          <t>Campbell River</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>Cortes Island</t>
+          <t>Frederick Arm (mainland)</t>
         </is>
       </c>
       <c r="J315" t="b">
@@ -18613,7 +18613,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>water-taxi:wt029</t>
+          <t>water-taxi:wt028</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -18623,17 +18623,17 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Terracentric Coastal Adventures</t>
+          <t>Sutil Charters</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>Lund – Cortes Island</t>
+          <t>Quadra Island – Cortes Island</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>qathet (Powell River) / Sunshine Coast</t>
+          <t>Strathcona / Discovery Islands</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -18641,7 +18641,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Lund</t>
+          <t>Quadra Island</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -18669,7 +18669,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>water-taxi:wt030</t>
+          <t>water-taxi:wt029</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -18679,30 +18679,30 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Shorebird Expeditions</t>
+          <t>Terracentric Coastal Adventures</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Tahsis – Yuquot (Friendly Cove)</t>
+          <t>Lund – Cortes Island</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Strathcona / West Coast Vancouver Island (Nootka Sound)</t>
+          <t>qathet (Powell River) / Sunshine Coast</t>
         </is>
       </c>
       <c r="G317" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>Tahsis</t>
+          <t>Lund</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>Yuquot / Friendly Cove (Nootka Island)</t>
+          <t>Cortes Island</t>
         </is>
       </c>
       <c r="J317" t="b">
@@ -18725,7 +18725,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>water-taxi:wt031</t>
+          <t>water-taxi:wt030</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -18735,12 +18735,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Nootka Water Taxi</t>
+          <t>Shorebird Expeditions</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Gold River – Yuquot (Friendly Cove)</t>
+          <t>Tahsis – Yuquot (Friendly Cove)</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -18753,12 +18753,12 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Gold River</t>
+          <t>Tahsis</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t>Hesquiat Peninsula</t>
+          <t>Yuquot / Friendly Cove (Nootka Island)</t>
         </is>
       </c>
       <c r="J318" t="b">
@@ -18781,7 +18781,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>water-taxi:wt032</t>
+          <t>water-taxi:wt031</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -18791,30 +18791,30 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Zeballos Expeditions (Zeballos Water Taxi)</t>
+          <t>Nootka Water Taxi</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Zeballos – Nuchatlitz / Nootka Island</t>
+          <t>Gold River – Yuquot (Friendly Cove)</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Strathcona / West Coast Vancouver Island (Esperanza-Nootka)</t>
+          <t>Strathcona / West Coast Vancouver Island (Nootka Sound)</t>
         </is>
       </c>
       <c r="G319" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>Zeballos</t>
+          <t>Gold River</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>Louie Bay (Nootka Island)</t>
+          <t>Hesquiat Peninsula</t>
         </is>
       </c>
       <c r="J319" t="b">
@@ -18837,7 +18837,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>water-taxi:wt033</t>
+          <t>water-taxi:wt032</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -18847,30 +18847,30 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>West Coast Launch</t>
+          <t>Zeballos Expeditions (Zeballos Water Taxi)</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>Kitimat – Hartley Bay</t>
+          <t>Zeballos – Nuchatlitz / Nootka Island</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>North Coast / Kitimat-Stikine</t>
+          <t>Strathcona / West Coast Vancouver Island (Esperanza-Nootka)</t>
         </is>
       </c>
       <c r="G320" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Kitimat</t>
+          <t>Zeballos</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>Kemano</t>
+          <t>Louie Bay (Nootka Island)</t>
         </is>
       </c>
       <c r="J320" t="b">
@@ -18889,16 +18889,11 @@
           <t>unknown</t>
         </is>
       </c>
-      <c r="N320" t="inlineStr">
-        <is>
-          <t>About 1.5–2 hours down Douglas Channel; call to arrange.</t>
-        </is>
-      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>water-taxi:wt034</t>
+          <t>water-taxi:wt033</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -18913,37 +18908,37 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Cow Bay (Prince Rupert) – Kitkatla (Gitxaała)</t>
+          <t>Kitimat – Hartley Bay</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>North Coast</t>
-        </is>
-      </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>limited</t>
+          <t>North Coast / Kitimat-Stikine</t>
         </is>
       </c>
       <c r="G321" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Kitimat</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>Kitkatla (Gitxaała)</t>
+          <t>Kemano</t>
         </is>
       </c>
       <c r="J321" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
       </c>
       <c r="L321" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M321" t="inlineStr">
         <is>
@@ -18952,14 +18947,14 @@
       </c>
       <c r="N321" t="inlineStr">
         <is>
-          <t>Twice-weekly ferry run in partnership with Gitxaała (Fridays 11am, Sundays noon); about 1.5–2 hours.</t>
+          <t>About 1.5–2 hours down Douglas Channel; call to arrange.</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>water-taxi:wt035</t>
+          <t>water-taxi:wt034</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -18974,7 +18969,7 @@
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Cow Bay (Prince Rupert) – Lax Kw'alaams (Port Simpson)</t>
+          <t>Cow Bay (Prince Rupert) – Kitkatla (Gitxaała)</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
@@ -18982,8 +18977,13 @@
           <t>North Coast</t>
         </is>
       </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
       <c r="G322" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H322" t="inlineStr">
         <is>
@@ -18992,19 +18992,14 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>Ketchikan (Alaska, USA)</t>
+          <t>Kitkatla (Gitxaała)</t>
         </is>
       </c>
       <c r="J322" t="b">
-        <v>0</v>
-      </c>
-      <c r="K322" t="inlineStr">
-        <is>
-          <t>charter only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L322" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M322" t="inlineStr">
         <is>
@@ -19013,14 +19008,14 @@
       </c>
       <c r="N322" t="inlineStr">
         <is>
-          <t>Call to arrange; also serves Gingolx and the Khutzeymateen.</t>
+          <t>Twice-weekly ferry run in partnership with Gitxaała (Fridays 11am, Sundays noon); about 1.5–2 hours.</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>water-taxi:wt036</t>
+          <t>water-taxi:wt035</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -19030,12 +19025,12 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Tsimshian Storm (Kitkatla/Hartley Bay/Metlakatla)</t>
+          <t>West Coast Launch</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Prince Rupert (Metlakatla dock) – Kitkatla</t>
+          <t>Cow Bay (Prince Rupert) – Lax Kw'alaams (Port Simpson)</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
@@ -19043,13 +19038,8 @@
           <t>North Coast</t>
         </is>
       </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>limited</t>
-        </is>
-      </c>
       <c r="G323" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H323" t="inlineStr">
         <is>
@@ -19058,14 +19048,19 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>Kitkatla (Gitxaała)</t>
+          <t>Ketchikan (Alaska, USA)</t>
         </is>
       </c>
       <c r="J323" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>charter only, not a scheduled service</t>
+        </is>
       </c>
       <c r="L323" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M323" t="inlineStr">
         <is>
@@ -19074,14 +19069,14 @@
       </c>
       <c r="N323" t="inlineStr">
         <is>
-          <t>Departs Prince Rupert twice weekly at 10am, returning from Kitkatla at noon; sailings are weather-dependent.</t>
+          <t>Call to arrange; also serves Gingolx and the Khutzeymateen.</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>water-taxi:wt037</t>
+          <t>water-taxi:wt036</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -19091,58 +19086,58 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>SeaCoastal Water Taxi (Kitasoo Xai'xais)</t>
+          <t>Tsimshian Storm (Kitkatla/Hartley Bay/Metlakatla)</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>Klemtu / Bella Bella – Central Coast communities</t>
+          <t>Prince Rupert (Metlakatla dock) – Kitkatla</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Central Coast (Great Bear Rainforest)</t>
+          <t>North Coast</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>on-demand</t>
+          <t>limited</t>
         </is>
       </c>
       <c r="G324" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>Klemtu</t>
+          <t>Prince Rupert</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>Prince Rupert</t>
+          <t>Kitkatla (Gitxaała)</t>
         </is>
       </c>
       <c r="J324" t="b">
-        <v>0</v>
-      </c>
-      <c r="K324" t="inlineStr">
-        <is>
-          <t>on demand only, not a scheduled service</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="L324" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M324" t="inlineStr">
         <is>
           <t>unknown</t>
+        </is>
+      </c>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>Departs Prince Rupert twice weekly at 10am, returning from Kitkatla at noon; sailings are weather-dependent.</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>water-taxi:wt038</t>
+          <t>water-taxi:wt037</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -19152,58 +19147,58 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>MV Uchuck III (Nootka Sound Service Ltd / Get West)</t>
+          <t>SeaCoastal Water Taxi (Kitasoo Xai'xais)</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>Gold River – Tahsis</t>
+          <t>Klemtu / Bella Bella – Central Coast communities</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Strathcona / West Coast Vancouver Island (Nootka Sound)</t>
+          <t>Central Coast (Great Bear Rainforest)</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>limited</t>
+          <t>on-demand</t>
         </is>
       </c>
       <c r="G325" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Gold River</t>
+          <t>Klemtu</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>Tahsis</t>
+          <t>Prince Rupert</t>
         </is>
       </c>
       <c r="J325" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>on demand only, not a scheduled service</t>
+        </is>
       </c>
       <c r="L325" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M325" t="inlineStr">
         <is>
           <t>unknown</t>
-        </is>
-      </c>
-      <c r="N325" t="inlineStr">
-        <is>
-          <t>A working coastal freighter that takes passengers; Nootka Sound day trips most Tuesdays.</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>water-taxi:wt039</t>
+          <t>water-taxi:wt038</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -19218,7 +19213,7 @@
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>Gold River – Yuquot (Friendly Cove)</t>
+          <t>Gold River – Tahsis</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
@@ -19241,7 +19236,7 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>Yuquot / Friendly Cove (Nootka Island)</t>
+          <t>Tahsis</t>
         </is>
       </c>
       <c r="J326" t="b">
@@ -19257,66 +19252,127 @@
       </c>
       <c r="N326" t="inlineStr">
         <is>
-          <t>Wednesday and Saturday sailings pick up Nootka Trail hikers at Friendly Cove, late June to early September.</t>
+          <t>A working coastal freighter that takes passengers; Nootka Sound day trips most Tuesdays.</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
+          <t>water-taxi:wt039</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>water-taxi</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>MV Uchuck III (Nootka Sound Service Ltd / Get West)</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Gold River – Yuquot (Friendly Cove)</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Strathcona / West Coast Vancouver Island (Nootka Sound)</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>limited</t>
+        </is>
+      </c>
+      <c r="G327" t="n">
+        <v>2</v>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>Gold River</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Yuquot / Friendly Cove (Nootka Island)</t>
+        </is>
+      </c>
+      <c r="J327" t="b">
+        <v>1</v>
+      </c>
+      <c r="L327" t="b">
+        <v>1</v>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>Wednesday and Saturday sailings pick up Nootka Trail hikers at Friendly Cove, late June to early September.</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
           <t>water-taxi:wt040</t>
         </is>
       </c>
-      <c r="B327" t="inlineStr">
+      <c r="B328" t="inlineStr">
         <is>
           <t>water-taxi</t>
         </is>
       </c>
-      <c r="C327" t="inlineStr">
+      <c r="C328" t="inlineStr">
         <is>
           <t>MV Uchuck III (Nootka Sound Service Ltd / Get West)</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr">
+      <c r="D328" t="inlineStr">
         <is>
           <t>Gold River – Kyuquot</t>
         </is>
       </c>
-      <c r="E327" t="inlineStr">
+      <c r="E328" t="inlineStr">
         <is>
           <t>Strathcona / West Coast Vancouver Island (Nootka–Kyuquot)</t>
         </is>
       </c>
-      <c r="F327" t="inlineStr">
+      <c r="F328" t="inlineStr">
         <is>
           <t>limited</t>
         </is>
       </c>
-      <c r="G327" t="n">
+      <c r="G328" t="n">
         <v>4</v>
       </c>
-      <c r="H327" t="inlineStr">
+      <c r="H328" t="inlineStr">
         <is>
           <t>Gold River</t>
         </is>
       </c>
-      <c r="I327" t="inlineStr">
+      <c r="I328" t="inlineStr">
         <is>
           <t>Kyuquot</t>
         </is>
       </c>
-      <c r="J327" t="b">
-        <v>1</v>
-      </c>
-      <c r="L327" t="b">
-        <v>1</v>
-      </c>
-      <c r="M327" t="inlineStr">
+      <c r="J328" t="b">
+        <v>1</v>
+      </c>
+      <c r="L328" t="b">
+        <v>1</v>
+      </c>
+      <c r="M328" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="N327" t="inlineStr">
+      <c r="N328" t="inlineStr">
         <is>
           <t>Overnight run to Kyuquot via Esperanza Inlet, Thursday to Friday, June to September.</t>
         </is>

--- a/research/files/bc_transit_routes.xlsx
+++ b/research/files/bc_transit_routes.xlsx
@@ -462,7 +462,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Published 2026-07-26 by BC Cycle Tourism Society.</t>
+          <t>Published 2026-08-11 by BC Cycle Tourism Society.</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Suggested citation: BC Cycle Tourism Society (2026). British Columbia transit routes, for cyclists [data set]. Version 2026-07-26. https://bccycletourism.ca/research/</t>
+          <t>Suggested citation: BC Cycle Tourism Society (2026). British Columbia transit routes, for cyclists [data set]. Version 2026-08-11. https://bccycletourism.ca/research/</t>
         </is>
       </c>
     </row>

--- a/research/files/bc_transit_routes.xlsx
+++ b/research/files/bc_transit_routes.xlsx
@@ -6885,7 +6885,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -10283,7 +10283,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -10578,7 +10578,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -10756,7 +10756,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -10812,7 +10812,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -10868,7 +10868,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -10924,7 +10924,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -11036,7 +11036,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -11092,7 +11092,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -11148,7 +11148,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -11265,7 +11265,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -11321,7 +11321,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -11382,7 +11382,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -11504,7 +11504,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -11560,7 +11560,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -11616,7 +11616,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -11672,7 +11672,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -11728,7 +11728,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -11840,7 +11840,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -11896,7 +11896,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -12135,7 +12135,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -12313,7 +12313,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -12430,7 +12430,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -12552,7 +12552,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -12608,7 +12608,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -12669,7 +12669,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -12847,7 +12847,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -12903,7 +12903,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -13020,7 +13020,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -13076,7 +13076,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -13132,7 +13132,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13188,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -13600,7 +13600,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -13661,7 +13661,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -13722,7 +13722,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -13778,7 +13778,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -13890,7 +13890,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -14358,7 +14358,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -14419,7 +14419,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -14475,7 +14475,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -14643,7 +14643,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -14765,7 +14765,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -14821,7 +14821,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -14999,7 +14999,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -15060,7 +15060,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -15121,7 +15121,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -15243,7 +15243,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -15355,7 +15355,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -15477,7 +15477,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -15538,7 +15538,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -15599,7 +15599,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -15655,7 +15655,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -15711,7 +15711,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -15833,7 +15833,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -15894,7 +15894,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -16016,7 +16016,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -16077,7 +16077,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes, with conditions</t>
         </is>
       </c>
     </row>

--- a/research/files/bc_transit_routes.xlsx
+++ b/research/files/bc_transit_routes.xlsx
@@ -462,7 +462,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Published 2026-08-11 by BC Cycle Tourism Society.</t>
+          <t>Published 2026-09-02 by BC Cycle Tourism Society.</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Suggested citation: BC Cycle Tourism Society (2026). British Columbia transit routes, for cyclists [data set]. Version 2026-08-11. https://bccycletourism.ca/research/</t>
+          <t>Suggested citation: BC Cycle Tourism Society (2026). British Columbia transit routes, for cyclists [data set]. Version 2026-09-02. https://bccycletourism.ca/research/</t>
         </is>
       </c>
     </row>
